--- a/companies/alder-ridge/source-files/Shared/Finance/FP&A/Backlog/FY27 backlog burn and capacity - WORKING.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/FP&A/Backlog/FY27 backlog burn and capacity - WORKING.xlsx
@@ -2,12 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Backlog" sheetId="1" r:id="Rbd597e9e190a4dbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Inputs" sheetId="2" r:id="R5c5e86bbb9de4298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Burn" sheetId="3" r:id="R6b5615d99d5a4895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor Capacity" sheetId="4" r:id="Re551e654c413420f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="5" r:id="Rb15210633c1d439e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" r:id="R27ef39dcb92342d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Backlog" sheetId="1" r:id="R90adb9c2d0964e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Inputs" sheetId="2" r:id="R6176971d7bd54b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Authority" sheetId="3" r:id="R68d9e667df264edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Burn" sheetId="4" r:id="Rea1d39ada1cd4a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor Capacity" sheetId="5" r:id="Rb682917fa0e74c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="6" r:id="R6f700491523f4ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Execution" sheetId="7" r:id="R950509ee15ef4959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R327d31c450c44878"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,8 +57,9 @@
       <x:name val="Aptos"/>
     </x:font>
     <x:font>
-      <x:sz val="9"/>
-      <x:color rgb="FF52655C"/>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF2A4337"/>
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
@@ -157,20 +160,20 @@
       <x:top style="thin">
         <x:color rgb="FFD8D0C6"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD8D0C6"/>
-      </x:bottom>
     </x:border>
     <x:border>
       <x:top style="thin">
         <x:color rgb="FFD8D0C6"/>
       </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8D0C6"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="52">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -236,18 +239,47 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -257,7 +289,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{8B34ECC0-75B2-4E54-9B02-CB456835F970}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{4F0CFD4D-9CDB-4176-9E2A-5A351BEAA3FF}"/>
 </xltc:personList>
 </file>
 
@@ -678,7 +710,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="23" t="str">
-        <x:v>035-SRC0005</x:v>
+        <x:v>035-SRC0008</x:v>
       </x:c>
       <x:c r="B9" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -712,7 +744,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="23" t="str">
-        <x:v>035-SRC0006</x:v>
+        <x:v>035-SRC0009</x:v>
       </x:c>
       <x:c r="B10" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -746,7 +778,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="23" t="str">
-        <x:v>035-SRC0007</x:v>
+        <x:v>035-SRC0010</x:v>
       </x:c>
       <x:c r="B11" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -780,7 +812,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="23" t="str">
-        <x:v>035-SRC0008</x:v>
+        <x:v>035-SRC0011</x:v>
       </x:c>
       <x:c r="B12" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -814,7 +846,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="23" t="str">
-        <x:v>035-SRC0009</x:v>
+        <x:v>035-SRC0012</x:v>
       </x:c>
       <x:c r="B13" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -848,7 +880,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="23" t="str">
-        <x:v>035-SRC0010</x:v>
+        <x:v>035-SRC0013</x:v>
       </x:c>
       <x:c r="B14" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -882,7 +914,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="23" t="str">
-        <x:v>035-SRC0011</x:v>
+        <x:v>035-SRC0014</x:v>
       </x:c>
       <x:c r="B15" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -916,7 +948,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="23" t="str">
-        <x:v>035-SRC0012</x:v>
+        <x:v>035-SRC0015</x:v>
       </x:c>
       <x:c r="B16" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -950,7 +982,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="23" t="str">
-        <x:v>035-SRC0013</x:v>
+        <x:v>035-SRC0016</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -984,7 +1016,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="23" t="str">
-        <x:v>035-SRC0014</x:v>
+        <x:v>035-SRC0017</x:v>
       </x:c>
       <x:c r="B18" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1018,7 +1050,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="23" t="str">
-        <x:v>035-SRC0015</x:v>
+        <x:v>035-SRC0018</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1052,7 +1084,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="23" t="str">
-        <x:v>035-SRC0016</x:v>
+        <x:v>035-SRC0019</x:v>
       </x:c>
       <x:c r="B20" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1086,7 +1118,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="23" t="str">
-        <x:v>035-SRC0017</x:v>
+        <x:v>035-SRC0020</x:v>
       </x:c>
       <x:c r="B21" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1104,11 +1136,11 @@
         <x:v>Remaining transaction price</x:v>
       </x:c>
       <x:c r="G21" s="26" t="n">
-        <x:v>6900000</x:v>
+        <x:v>6900</x:v>
       </x:c>
       <x:c r="H21" s="23" t="str"/>
       <x:c r="I21" s="23" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J21" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -1120,7 +1152,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="23" t="str">
-        <x:v>035-SRC0018</x:v>
+        <x:v>035-SRC0021</x:v>
       </x:c>
       <x:c r="B22" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1154,7 +1186,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="23" t="str">
-        <x:v>035-SRC0019</x:v>
+        <x:v>035-SRC0022</x:v>
       </x:c>
       <x:c r="B23" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1188,7 +1220,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="23" t="str">
-        <x:v>035-SRC0020</x:v>
+        <x:v>035-SRC0023</x:v>
       </x:c>
       <x:c r="B24" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1222,7 +1254,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="23" t="str">
-        <x:v>035-SRC0021</x:v>
+        <x:v>035-SRC0027</x:v>
       </x:c>
       <x:c r="B25" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1256,7 +1288,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="23" t="str">
-        <x:v>035-SRC0022</x:v>
+        <x:v>035-SRC0028</x:v>
       </x:c>
       <x:c r="B26" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1290,7 +1322,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="23" t="str">
-        <x:v>035-SRC0023</x:v>
+        <x:v>035-SRC0029</x:v>
       </x:c>
       <x:c r="B27" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1324,7 +1356,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="23" t="str">
-        <x:v>035-SRC0024</x:v>
+        <x:v>035-SRC0030</x:v>
       </x:c>
       <x:c r="B28" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1358,7 +1390,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="23" t="str">
-        <x:v>035-SRC0025</x:v>
+        <x:v>035-SRC0031</x:v>
       </x:c>
       <x:c r="B29" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1392,7 +1424,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="23" t="str">
-        <x:v>035-SRC0026</x:v>
+        <x:v>035-SRC0032</x:v>
       </x:c>
       <x:c r="B30" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1426,7 +1458,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="23" t="str">
-        <x:v>035-SRC0027</x:v>
+        <x:v>035-SRC0033</x:v>
       </x:c>
       <x:c r="B31" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1460,7 +1492,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="23" t="str">
-        <x:v>035-SRC0028</x:v>
+        <x:v>035-SRC0034</x:v>
       </x:c>
       <x:c r="B32" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1494,7 +1526,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="23" t="str">
-        <x:v>035-SRC0029</x:v>
+        <x:v>035-SRC0035</x:v>
       </x:c>
       <x:c r="B33" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1528,7 +1560,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="23" t="str">
-        <x:v>035-SRC0030</x:v>
+        <x:v>035-SRC0036</x:v>
       </x:c>
       <x:c r="B34" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1562,7 +1594,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="23" t="str">
-        <x:v>035-SRC0031</x:v>
+        <x:v>035-SRC0037</x:v>
       </x:c>
       <x:c r="B35" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1596,7 +1628,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="23" t="str">
-        <x:v>035-SRC0032</x:v>
+        <x:v>035-SRC0038</x:v>
       </x:c>
       <x:c r="B36" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1614,11 +1646,11 @@
         <x:v>Remaining transaction price</x:v>
       </x:c>
       <x:c r="G36" s="26" t="n">
-        <x:v>5600</x:v>
+        <x:v>5600000</x:v>
       </x:c>
       <x:c r="H36" s="23" t="str"/>
       <x:c r="I36" s="23" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="J36" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -1630,7 +1662,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="23" t="str">
-        <x:v>035-SRC0033</x:v>
+        <x:v>035-SRC0039</x:v>
       </x:c>
       <x:c r="B37" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1664,7 +1696,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="23" t="str">
-        <x:v>035-SRC0034</x:v>
+        <x:v>035-SRC0040</x:v>
       </x:c>
       <x:c r="B38" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1698,7 +1730,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="23" t="str">
-        <x:v>035-SRC0035</x:v>
+        <x:v>035-SRC0041</x:v>
       </x:c>
       <x:c r="B39" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -1732,7 +1764,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="23" t="str">
-        <x:v>035-SRC0036</x:v>
+        <x:v>035-SRC0045</x:v>
       </x:c>
       <x:c r="B40" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1766,7 +1798,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="23" t="str">
-        <x:v>035-SRC0037</x:v>
+        <x:v>035-SRC0046</x:v>
       </x:c>
       <x:c r="B41" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1800,7 +1832,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="23" t="str">
-        <x:v>035-SRC0038</x:v>
+        <x:v>035-SRC0047</x:v>
       </x:c>
       <x:c r="B42" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1834,7 +1866,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="23" t="str">
-        <x:v>035-SRC0039</x:v>
+        <x:v>035-SRC0048</x:v>
       </x:c>
       <x:c r="B43" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1868,7 +1900,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="23" t="str">
-        <x:v>035-SRC0040</x:v>
+        <x:v>035-SRC0049</x:v>
       </x:c>
       <x:c r="B44" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1902,7 +1934,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="23" t="str">
-        <x:v>035-SRC0041</x:v>
+        <x:v>035-SRC0050</x:v>
       </x:c>
       <x:c r="B45" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1936,7 +1968,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="23" t="str">
-        <x:v>035-SRC0042</x:v>
+        <x:v>035-SRC0051</x:v>
       </x:c>
       <x:c r="B46" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -1970,7 +2002,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="23" t="str">
-        <x:v>035-SRC0043</x:v>
+        <x:v>035-SRC0052</x:v>
       </x:c>
       <x:c r="B47" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2004,7 +2036,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="23" t="str">
-        <x:v>035-SRC0044</x:v>
+        <x:v>035-SRC0053</x:v>
       </x:c>
       <x:c r="B48" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2038,7 +2070,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="23" t="str">
-        <x:v>035-SRC0045</x:v>
+        <x:v>035-SRC0054</x:v>
       </x:c>
       <x:c r="B49" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2072,7 +2104,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="23" t="str">
-        <x:v>035-SRC0046</x:v>
+        <x:v>035-SRC0055</x:v>
       </x:c>
       <x:c r="B50" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2106,7 +2138,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="23" t="str">
-        <x:v>035-SRC0047</x:v>
+        <x:v>035-SRC0056</x:v>
       </x:c>
       <x:c r="B51" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2140,7 +2172,7 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="23" t="str">
-        <x:v>035-SRC0048</x:v>
+        <x:v>035-SRC0057</x:v>
       </x:c>
       <x:c r="B52" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2174,7 +2206,7 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="23" t="str">
-        <x:v>035-SRC0049</x:v>
+        <x:v>035-SRC0061</x:v>
       </x:c>
       <x:c r="B53" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2208,7 +2240,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="23" t="str">
-        <x:v>035-SRC0050</x:v>
+        <x:v>035-SRC0062</x:v>
       </x:c>
       <x:c r="B54" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2242,7 +2274,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="23" t="str">
-        <x:v>035-SRC0051</x:v>
+        <x:v>035-SRC0063</x:v>
       </x:c>
       <x:c r="B55" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2276,7 +2308,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="23" t="str">
-        <x:v>035-SRC0052</x:v>
+        <x:v>035-SRC0064</x:v>
       </x:c>
       <x:c r="B56" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2310,7 +2342,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="23" t="str">
-        <x:v>035-SRC0053</x:v>
+        <x:v>035-SRC0065</x:v>
       </x:c>
       <x:c r="B57" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2344,7 +2376,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="23" t="str">
-        <x:v>035-SRC0054</x:v>
+        <x:v>035-SRC0066</x:v>
       </x:c>
       <x:c r="B58" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2378,7 +2410,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="23" t="str">
-        <x:v>035-SRC0055</x:v>
+        <x:v>035-SRC0067</x:v>
       </x:c>
       <x:c r="B59" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2412,7 +2444,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="23" t="str">
-        <x:v>035-SRC0056</x:v>
+        <x:v>035-SRC0068</x:v>
       </x:c>
       <x:c r="B60" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2446,7 +2478,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="23" t="str">
-        <x:v>035-SRC0057</x:v>
+        <x:v>035-SRC0069</x:v>
       </x:c>
       <x:c r="B61" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2480,7 +2512,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="23" t="str">
-        <x:v>035-SRC0058</x:v>
+        <x:v>035-SRC0070</x:v>
       </x:c>
       <x:c r="B62" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2514,7 +2546,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="23" t="str">
-        <x:v>035-SRC0059</x:v>
+        <x:v>035-SRC0071</x:v>
       </x:c>
       <x:c r="B63" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2548,7 +2580,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="23" t="str">
-        <x:v>035-SRC0060</x:v>
+        <x:v>035-SRC0075</x:v>
       </x:c>
       <x:c r="B64" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2582,7 +2614,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="23" t="str">
-        <x:v>035-SRC0061</x:v>
+        <x:v>035-SRC0076</x:v>
       </x:c>
       <x:c r="B65" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2616,7 +2648,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="23" t="str">
-        <x:v>035-SRC0062</x:v>
+        <x:v>035-SRC0077</x:v>
       </x:c>
       <x:c r="B66" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2650,7 +2682,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="23" t="str">
-        <x:v>035-SRC0063</x:v>
+        <x:v>035-SRC0078</x:v>
       </x:c>
       <x:c r="B67" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2684,7 +2716,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="23" t="str">
-        <x:v>035-SRC0064</x:v>
+        <x:v>035-SRC0079</x:v>
       </x:c>
       <x:c r="B68" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2718,7 +2750,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="23" t="str">
-        <x:v>035-SRC0065</x:v>
+        <x:v>035-SRC0080</x:v>
       </x:c>
       <x:c r="B69" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2752,7 +2784,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="23" t="str">
-        <x:v>035-SRC0066</x:v>
+        <x:v>035-SRC0081</x:v>
       </x:c>
       <x:c r="B70" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2786,7 +2818,7 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="23" t="str">
-        <x:v>035-SRC0067</x:v>
+        <x:v>035-SRC0082</x:v>
       </x:c>
       <x:c r="B71" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2820,7 +2852,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="23" t="str">
-        <x:v>035-SRC0068</x:v>
+        <x:v>035-SRC0083</x:v>
       </x:c>
       <x:c r="B72" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2854,7 +2886,7 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="23" t="str">
-        <x:v>035-SRC0069</x:v>
+        <x:v>035-SRC0084</x:v>
       </x:c>
       <x:c r="B73" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -2888,7 +2920,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="23" t="str">
-        <x:v>035-SRC0070</x:v>
+        <x:v>035-SRC0088</x:v>
       </x:c>
       <x:c r="B74" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2922,7 +2954,7 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="23" t="str">
-        <x:v>035-SRC0071</x:v>
+        <x:v>035-SRC0089</x:v>
       </x:c>
       <x:c r="B75" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2956,7 +2988,7 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="23" t="str">
-        <x:v>035-SRC0072</x:v>
+        <x:v>035-SRC0090</x:v>
       </x:c>
       <x:c r="B76" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -2990,7 +3022,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="23" t="str">
-        <x:v>035-SRC0073</x:v>
+        <x:v>035-SRC0091</x:v>
       </x:c>
       <x:c r="B77" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3024,7 +3056,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="23" t="str">
-        <x:v>035-SRC0074</x:v>
+        <x:v>035-SRC0092</x:v>
       </x:c>
       <x:c r="B78" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3058,7 +3090,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="23" t="str">
-        <x:v>035-SRC0075</x:v>
+        <x:v>035-SRC0093</x:v>
       </x:c>
       <x:c r="B79" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3092,7 +3124,7 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="23" t="str">
-        <x:v>035-SRC0076</x:v>
+        <x:v>035-SRC0094</x:v>
       </x:c>
       <x:c r="B80" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3126,7 +3158,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="23" t="str">
-        <x:v>035-SRC0077</x:v>
+        <x:v>035-SRC0095</x:v>
       </x:c>
       <x:c r="B81" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3160,7 +3192,7 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="23" t="str">
-        <x:v>035-SRC0078</x:v>
+        <x:v>035-SRC0096</x:v>
       </x:c>
       <x:c r="B82" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3194,7 +3226,7 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="23" t="str">
-        <x:v>035-SRC0079</x:v>
+        <x:v>035-SRC0100</x:v>
       </x:c>
       <x:c r="B83" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3228,7 +3260,7 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="23" t="str">
-        <x:v>035-SRC0080</x:v>
+        <x:v>035-SRC0101</x:v>
       </x:c>
       <x:c r="B84" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3262,7 +3294,7 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="23" t="str">
-        <x:v>035-SRC0081</x:v>
+        <x:v>035-SRC0102</x:v>
       </x:c>
       <x:c r="B85" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3296,7 +3328,7 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="23" t="str">
-        <x:v>035-SRC0082</x:v>
+        <x:v>035-SRC0103</x:v>
       </x:c>
       <x:c r="B86" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3330,7 +3362,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="23" t="str">
-        <x:v>035-SRC0083</x:v>
+        <x:v>035-SRC0104</x:v>
       </x:c>
       <x:c r="B87" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3348,11 +3380,11 @@
         <x:v>Remaining transaction price</x:v>
       </x:c>
       <x:c r="G87" s="26" t="n">
-        <x:v>2850000</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="H87" s="23" t="str"/>
       <x:c r="I87" s="23" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J87" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -3364,7 +3396,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="23" t="str">
-        <x:v>035-SRC0084</x:v>
+        <x:v>035-SRC0105</x:v>
       </x:c>
       <x:c r="B88" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3398,7 +3430,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="23" t="str">
-        <x:v>035-SRC0085</x:v>
+        <x:v>035-SRC0106</x:v>
       </x:c>
       <x:c r="B89" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3432,7 +3464,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="23" t="str">
-        <x:v>035-SRC0086</x:v>
+        <x:v>035-SRC0107</x:v>
       </x:c>
       <x:c r="B90" s="23" t="str">
         <x:v>Signed contract backlog</x:v>
@@ -3466,7 +3498,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="23" t="str">
-        <x:v>035-SRC0087</x:v>
+        <x:v>035-SRC0111</x:v>
       </x:c>
       <x:c r="B91" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3500,7 +3532,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="23" t="str">
-        <x:v>035-SRC0088</x:v>
+        <x:v>035-SRC0112</x:v>
       </x:c>
       <x:c r="B92" s="23" t="str">
         <x:v>Project burn curve</x:v>
@@ -3534,7 +3566,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="24" t="str">
-        <x:v>035-SRC0089</x:v>
+        <x:v>035-SRC0113</x:v>
       </x:c>
       <x:c r="B93" s="24" t="str">
         <x:v>Project burn curve</x:v>
@@ -3665,7 +3697,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="22" t="str">
-        <x:v>035-SRC0090</x:v>
+        <x:v>035-SRC0114</x:v>
       </x:c>
       <x:c r="B5" s="22" t="str">
         <x:v>Monthly capacity</x:v>
@@ -3699,7 +3731,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="23" t="str">
-        <x:v>035-SRC0091</x:v>
+        <x:v>035-SRC0115</x:v>
       </x:c>
       <x:c r="B6" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -3733,7 +3765,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="23" t="str">
-        <x:v>035-SRC0092</x:v>
+        <x:v>035-SRC0116</x:v>
       </x:c>
       <x:c r="B7" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -3767,32 +3799,32 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
-        <x:v>035-SRC0093</x:v>
+        <x:v>035-SRC0117</x:v>
       </x:c>
       <x:c r="B8" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C8" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D8" s="23" t="str">
-        <x:v>2026-08</x:v>
+        <x:v>2026-07</x:v>
       </x:c>
       <x:c r="E8" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F8" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Emergency overtime increment limit</x:v>
       </x:c>
       <x:c r="G8" s="26" t="n">
-        <x:v>31780</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="H8" s="23" t="str"/>
       <x:c r="I8" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J8" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved capacity-response policy</x:v>
       </x:c>
       <x:c r="K8" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3801,32 +3833,32 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="23" t="str">
-        <x:v>035-SRC0094</x:v>
+        <x:v>035-SRC0118</x:v>
       </x:c>
       <x:c r="B9" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C9" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D9" s="23" t="str">
-        <x:v>2026-08</x:v>
+        <x:v>2026-07</x:v>
       </x:c>
       <x:c r="E9" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F9" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Contingent subcontract surge hours</x:v>
       </x:c>
       <x:c r="G9" s="26" t="n">
-        <x:v>4500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="H9" s="23" t="str"/>
       <x:c r="I9" s="23" t="str">
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J9" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K9" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3835,32 +3867,32 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="23" t="str">
-        <x:v>035-SRC0095</x:v>
+        <x:v>035-SRC0119</x:v>
       </x:c>
       <x:c r="B10" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C10" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D10" s="23" t="str">
-        <x:v>2026-08</x:v>
+        <x:v>2026-07</x:v>
       </x:c>
       <x:c r="E10" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F10" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Overtime premium cost</x:v>
       </x:c>
       <x:c r="G10" s="26" t="n">
-        <x:v>0.08</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="H10" s="23" t="str"/>
       <x:c r="I10" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J10" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved labor-cost assumptions</x:v>
       </x:c>
       <x:c r="K10" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3869,32 +3901,32 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="23" t="str">
-        <x:v>035-SRC0096</x:v>
+        <x:v>035-SRC0120</x:v>
       </x:c>
       <x:c r="B11" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C11" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D11" s="23" t="str">
-        <x:v>2026-09</x:v>
+        <x:v>2026-07</x:v>
       </x:c>
       <x:c r="E11" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F11" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Contingent subcontract cost</x:v>
       </x:c>
       <x:c r="G11" s="26" t="n">
-        <x:v>32060</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H11" s="23" t="str"/>
       <x:c r="I11" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J11" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K11" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -3903,7 +3935,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="23" t="str">
-        <x:v>035-SRC0097</x:v>
+        <x:v>035-SRC0121</x:v>
       </x:c>
       <x:c r="B12" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -3912,16 +3944,16 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D12" s="23" t="str">
-        <x:v>2026-09</x:v>
+        <x:v>2026-08</x:v>
       </x:c>
       <x:c r="E12" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F12" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Productive internal hours</x:v>
       </x:c>
       <x:c r="G12" s="26" t="n">
-        <x:v>4500</x:v>
+        <x:v>31780</x:v>
       </x:c>
       <x:c r="H12" s="23" t="str"/>
       <x:c r="I12" s="23" t="str">
@@ -3937,7 +3969,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="23" t="str">
-        <x:v>035-SRC0098</x:v>
+        <x:v>035-SRC0122</x:v>
       </x:c>
       <x:c r="B13" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -3946,20 +3978,20 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D13" s="23" t="str">
-        <x:v>2026-09</x:v>
+        <x:v>2026-08</x:v>
       </x:c>
       <x:c r="E13" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F13" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Subcontractable hours</x:v>
       </x:c>
       <x:c r="G13" s="26" t="n">
-        <x:v>0.08</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="H13" s="23" t="str"/>
       <x:c r="I13" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>hours</x:v>
       </x:c>
       <x:c r="J13" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -3971,7 +4003,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="23" t="str">
-        <x:v>035-SRC0099</x:v>
+        <x:v>035-SRC0123</x:v>
       </x:c>
       <x:c r="B14" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -3980,20 +4012,20 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D14" s="23" t="str">
-        <x:v>2026-10</x:v>
+        <x:v>2026-08</x:v>
       </x:c>
       <x:c r="E14" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F14" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Overtime limit on internal hours</x:v>
       </x:c>
       <x:c r="G14" s="26" t="n">
-        <x:v>32340</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="H14" s="23" t="str"/>
       <x:c r="I14" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J14" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -4005,32 +4037,32 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="23" t="str">
-        <x:v>035-SRC0100</x:v>
+        <x:v>035-SRC0124</x:v>
       </x:c>
       <x:c r="B15" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C15" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D15" s="23" t="str">
-        <x:v>2026-10</x:v>
+        <x:v>2026-08</x:v>
       </x:c>
       <x:c r="E15" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F15" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Emergency overtime increment limit</x:v>
       </x:c>
       <x:c r="G15" s="26" t="n">
-        <x:v>4500</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="H15" s="23" t="str"/>
       <x:c r="I15" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J15" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved capacity-response policy</x:v>
       </x:c>
       <x:c r="K15" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4039,32 +4071,32 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="23" t="str">
-        <x:v>035-SRC0101</x:v>
+        <x:v>035-SRC0125</x:v>
       </x:c>
       <x:c r="B16" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C16" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D16" s="23" t="str">
-        <x:v>2026-10</x:v>
+        <x:v>2026-08</x:v>
       </x:c>
       <x:c r="E16" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F16" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Contingent subcontract surge hours</x:v>
       </x:c>
       <x:c r="G16" s="26" t="n">
-        <x:v>0.08</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="H16" s="23" t="str"/>
       <x:c r="I16" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>hours</x:v>
       </x:c>
       <x:c r="J16" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K16" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4073,32 +4105,32 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="23" t="str">
-        <x:v>035-SRC0102</x:v>
+        <x:v>035-SRC0126</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C17" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D17" s="23" t="str">
-        <x:v>2026-11</x:v>
+        <x:v>2026-08</x:v>
       </x:c>
       <x:c r="E17" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F17" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Overtime premium cost</x:v>
       </x:c>
       <x:c r="G17" s="26" t="n">
-        <x:v>32620</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="H17" s="23" t="str"/>
       <x:c r="I17" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J17" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved labor-cost assumptions</x:v>
       </x:c>
       <x:c r="K17" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4107,32 +4139,32 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="23" t="str">
-        <x:v>035-SRC0103</x:v>
+        <x:v>035-SRC0127</x:v>
       </x:c>
       <x:c r="B18" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C18" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D18" s="23" t="str">
-        <x:v>2026-11</x:v>
+        <x:v>2026-08</x:v>
       </x:c>
       <x:c r="E18" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F18" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Contingent subcontract cost</x:v>
       </x:c>
       <x:c r="G18" s="26" t="n">
-        <x:v>4500</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H18" s="23" t="str"/>
       <x:c r="I18" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J18" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K18" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4141,7 +4173,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="23" t="str">
-        <x:v>035-SRC0104</x:v>
+        <x:v>035-SRC0128</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4150,20 +4182,20 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D19" s="23" t="str">
-        <x:v>2026-11</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E19" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F19" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Productive internal hours</x:v>
       </x:c>
       <x:c r="G19" s="26" t="n">
-        <x:v>0.08</x:v>
+        <x:v>32060</x:v>
       </x:c>
       <x:c r="H19" s="23" t="str"/>
       <x:c r="I19" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>hours</x:v>
       </x:c>
       <x:c r="J19" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -4175,7 +4207,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="23" t="str">
-        <x:v>035-SRC0105</x:v>
+        <x:v>035-SRC0129</x:v>
       </x:c>
       <x:c r="B20" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4184,16 +4216,16 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D20" s="23" t="str">
-        <x:v>2026-12</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E20" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F20" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Subcontractable hours</x:v>
       </x:c>
       <x:c r="G20" s="26" t="n">
-        <x:v>30100</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="H20" s="23" t="str"/>
       <x:c r="I20" s="23" t="str">
@@ -4209,7 +4241,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="23" t="str">
-        <x:v>035-SRC0106</x:v>
+        <x:v>035-SRC0130</x:v>
       </x:c>
       <x:c r="B21" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4218,20 +4250,20 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D21" s="23" t="str">
-        <x:v>2026-12</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E21" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F21" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Overtime limit on internal hours</x:v>
       </x:c>
       <x:c r="G21" s="26" t="n">
-        <x:v>4500</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="H21" s="23" t="str"/>
       <x:c r="I21" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J21" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -4243,32 +4275,32 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="23" t="str">
-        <x:v>035-SRC0107</x:v>
+        <x:v>035-SRC0131</x:v>
       </x:c>
       <x:c r="B22" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C22" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D22" s="23" t="str">
-        <x:v>2026-12</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E22" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F22" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Emergency overtime increment limit</x:v>
       </x:c>
       <x:c r="G22" s="26" t="n">
-        <x:v>0.08</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="H22" s="23" t="str"/>
       <x:c r="I22" s="23" t="str">
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J22" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved capacity-response policy</x:v>
       </x:c>
       <x:c r="K22" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4277,32 +4309,32 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="23" t="str">
-        <x:v>035-SRC0108</x:v>
+        <x:v>035-SRC0132</x:v>
       </x:c>
       <x:c r="B23" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C23" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D23" s="23" t="str">
-        <x:v>2027-01</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E23" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F23" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Contingent subcontract surge hours</x:v>
       </x:c>
       <x:c r="G23" s="26" t="n">
-        <x:v>30380</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="H23" s="23" t="str"/>
       <x:c r="I23" s="23" t="str">
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J23" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K23" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4311,32 +4343,32 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="23" t="str">
-        <x:v>035-SRC0109</x:v>
+        <x:v>035-SRC0133</x:v>
       </x:c>
       <x:c r="B24" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C24" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D24" s="23" t="str">
-        <x:v>2027-01</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E24" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F24" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Overtime premium cost</x:v>
       </x:c>
       <x:c r="G24" s="26" t="n">
-        <x:v>4500</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="H24" s="23" t="str"/>
       <x:c r="I24" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J24" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved labor-cost assumptions</x:v>
       </x:c>
       <x:c r="K24" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4345,32 +4377,32 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="23" t="str">
-        <x:v>035-SRC0110</x:v>
+        <x:v>035-SRC0134</x:v>
       </x:c>
       <x:c r="B25" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C25" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D25" s="23" t="str">
-        <x:v>2027-01</x:v>
+        <x:v>2026-09</x:v>
       </x:c>
       <x:c r="E25" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F25" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Contingent subcontract cost</x:v>
       </x:c>
       <x:c r="G25" s="26" t="n">
-        <x:v>0.08</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H25" s="23" t="str"/>
       <x:c r="I25" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J25" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K25" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4379,7 +4411,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="23" t="str">
-        <x:v>035-SRC0111</x:v>
+        <x:v>035-SRC0135</x:v>
       </x:c>
       <x:c r="B26" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4388,7 +4420,7 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D26" s="23" t="str">
-        <x:v>2027-02</x:v>
+        <x:v>2026-10</x:v>
       </x:c>
       <x:c r="E26" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -4397,7 +4429,7 @@
         <x:v>Productive internal hours</x:v>
       </x:c>
       <x:c r="G26" s="26" t="n">
-        <x:v>33460</x:v>
+        <x:v>32340</x:v>
       </x:c>
       <x:c r="H26" s="23" t="str"/>
       <x:c r="I26" s="23" t="str">
@@ -4413,7 +4445,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="23" t="str">
-        <x:v>035-SRC0112</x:v>
+        <x:v>035-SRC0136</x:v>
       </x:c>
       <x:c r="B27" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4422,7 +4454,7 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D27" s="23" t="str">
-        <x:v>2027-02</x:v>
+        <x:v>2026-10</x:v>
       </x:c>
       <x:c r="E27" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -4431,7 +4463,7 @@
         <x:v>Subcontractable hours</x:v>
       </x:c>
       <x:c r="G27" s="26" t="n">
-        <x:v>3200</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="H27" s="23" t="str"/>
       <x:c r="I27" s="23" t="str">
@@ -4447,7 +4479,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="23" t="str">
-        <x:v>035-SRC0113</x:v>
+        <x:v>035-SRC0137</x:v>
       </x:c>
       <x:c r="B28" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4456,7 +4488,7 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D28" s="23" t="str">
-        <x:v>2027-02</x:v>
+        <x:v>2026-10</x:v>
       </x:c>
       <x:c r="E28" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -4481,32 +4513,32 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="23" t="str">
-        <x:v>035-SRC0114</x:v>
+        <x:v>035-SRC0138</x:v>
       </x:c>
       <x:c r="B29" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C29" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D29" s="23" t="str">
-        <x:v>2027-03</x:v>
+        <x:v>2026-10</x:v>
       </x:c>
       <x:c r="E29" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F29" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Emergency overtime increment limit</x:v>
       </x:c>
       <x:c r="G29" s="26" t="n">
-        <x:v>33740</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="H29" s="23" t="str"/>
       <x:c r="I29" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J29" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved capacity-response policy</x:v>
       </x:c>
       <x:c r="K29" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4515,32 +4547,32 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="23" t="str">
-        <x:v>035-SRC0115</x:v>
+        <x:v>035-SRC0139</x:v>
       </x:c>
       <x:c r="B30" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C30" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D30" s="23" t="str">
-        <x:v>2027-03</x:v>
+        <x:v>2026-10</x:v>
       </x:c>
       <x:c r="E30" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F30" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Contingent subcontract surge hours</x:v>
       </x:c>
       <x:c r="G30" s="26" t="n">
-        <x:v>3200</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="H30" s="23" t="str"/>
       <x:c r="I30" s="23" t="str">
         <x:v>hours</x:v>
       </x:c>
       <x:c r="J30" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K30" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4549,32 +4581,32 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="23" t="str">
-        <x:v>035-SRC0116</x:v>
+        <x:v>035-SRC0140</x:v>
       </x:c>
       <x:c r="B31" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C31" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D31" s="23" t="str">
-        <x:v>2027-03</x:v>
+        <x:v>2026-10</x:v>
       </x:c>
       <x:c r="E31" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Overtime premium cost</x:v>
       </x:c>
       <x:c r="G31" s="26" t="n">
-        <x:v>0.05</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="H31" s="23" t="str"/>
       <x:c r="I31" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J31" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved labor-cost assumptions</x:v>
       </x:c>
       <x:c r="K31" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4583,32 +4615,32 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="23" t="str">
-        <x:v>035-SRC0117</x:v>
+        <x:v>035-SRC0141</x:v>
       </x:c>
       <x:c r="B32" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C32" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D32" s="23" t="str">
-        <x:v>2027-04</x:v>
+        <x:v>2026-10</x:v>
       </x:c>
       <x:c r="E32" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F32" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Contingent subcontract cost</x:v>
       </x:c>
       <x:c r="G32" s="26" t="n">
-        <x:v>34020</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H32" s="23" t="str"/>
       <x:c r="I32" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J32" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K32" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4617,7 +4649,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="23" t="str">
-        <x:v>035-SRC0118</x:v>
+        <x:v>035-SRC0142</x:v>
       </x:c>
       <x:c r="B33" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4626,16 +4658,16 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D33" s="23" t="str">
-        <x:v>2027-04</x:v>
+        <x:v>2026-11</x:v>
       </x:c>
       <x:c r="E33" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F33" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Productive internal hours</x:v>
       </x:c>
       <x:c r="G33" s="26" t="n">
-        <x:v>3200</x:v>
+        <x:v>32620</x:v>
       </x:c>
       <x:c r="H33" s="23" t="str"/>
       <x:c r="I33" s="23" t="str">
@@ -4651,7 +4683,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="23" t="str">
-        <x:v>035-SRC0119</x:v>
+        <x:v>035-SRC0143</x:v>
       </x:c>
       <x:c r="B34" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4660,20 +4692,20 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D34" s="23" t="str">
-        <x:v>2027-04</x:v>
+        <x:v>2026-11</x:v>
       </x:c>
       <x:c r="E34" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F34" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Subcontractable hours</x:v>
       </x:c>
       <x:c r="G34" s="26" t="n">
-        <x:v>0.05</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="H34" s="23" t="str"/>
       <x:c r="I34" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>hours</x:v>
       </x:c>
       <x:c r="J34" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -4685,7 +4717,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="23" t="str">
-        <x:v>035-SRC0120</x:v>
+        <x:v>035-SRC0144</x:v>
       </x:c>
       <x:c r="B35" s="23" t="str">
         <x:v>Monthly capacity</x:v>
@@ -4694,20 +4726,20 @@
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D35" s="23" t="str">
-        <x:v>2027-05</x:v>
+        <x:v>2026-11</x:v>
       </x:c>
       <x:c r="E35" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F35" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Overtime limit on internal hours</x:v>
       </x:c>
       <x:c r="G35" s="26" t="n">
-        <x:v>34300</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="H35" s="23" t="str"/>
       <x:c r="I35" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J35" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -4719,32 +4751,32 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="23" t="str">
-        <x:v>035-SRC0121</x:v>
+        <x:v>035-SRC0145</x:v>
       </x:c>
       <x:c r="B36" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C36" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D36" s="23" t="str">
-        <x:v>2027-05</x:v>
+        <x:v>2026-11</x:v>
       </x:c>
       <x:c r="E36" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F36" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Emergency overtime increment limit</x:v>
       </x:c>
       <x:c r="G36" s="26" t="n">
-        <x:v>3200</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="H36" s="23" t="str"/>
       <x:c r="I36" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J36" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved capacity-response policy</x:v>
       </x:c>
       <x:c r="K36" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4753,32 +4785,32 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="23" t="str">
-        <x:v>035-SRC0122</x:v>
+        <x:v>035-SRC0146</x:v>
       </x:c>
       <x:c r="B37" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C37" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D37" s="23" t="str">
-        <x:v>2027-05</x:v>
+        <x:v>2026-11</x:v>
       </x:c>
       <x:c r="E37" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F37" s="23" t="str">
-        <x:v>Overtime limit on internal hours</x:v>
+        <x:v>Contingent subcontract surge hours</x:v>
       </x:c>
       <x:c r="G37" s="26" t="n">
-        <x:v>0.08</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="H37" s="23" t="str"/>
       <x:c r="I37" s="23" t="str">
-        <x:v>decimal ratio</x:v>
+        <x:v>hours</x:v>
       </x:c>
       <x:c r="J37" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Executed contingent labor framework</x:v>
       </x:c>
       <x:c r="K37" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4787,32 +4819,32 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="23" t="str">
-        <x:v>035-SRC0123</x:v>
+        <x:v>035-SRC0147</x:v>
       </x:c>
       <x:c r="B38" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C38" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D38" s="23" t="str">
-        <x:v>2027-06</x:v>
+        <x:v>2026-11</x:v>
       </x:c>
       <x:c r="E38" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F38" s="23" t="str">
-        <x:v>Productive internal hours</x:v>
+        <x:v>Overtime premium cost</x:v>
       </x:c>
       <x:c r="G38" s="26" t="n">
-        <x:v>34580</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="H38" s="23" t="str"/>
       <x:c r="I38" s="23" t="str">
-        <x:v>hours</x:v>
+        <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="J38" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved labor-cost assumptions</x:v>
       </x:c>
       <x:c r="K38" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -4821,71 +4853,1703 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="23" t="str">
-        <x:v>035-SRC0124</x:v>
+        <x:v>035-SRC0148</x:v>
       </x:c>
       <x:c r="B39" s="23" t="str">
-        <x:v>Monthly capacity</x:v>
+        <x:v>Capacity remediation</x:v>
       </x:c>
       <x:c r="C39" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
       <x:c r="D39" s="23" t="str">
-        <x:v>2027-06</x:v>
+        <x:v>2026-11</x:v>
       </x:c>
       <x:c r="E39" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F39" s="23" t="str">
-        <x:v>Subcontractable hours</x:v>
+        <x:v>Contingent subcontract cost</x:v>
       </x:c>
       <x:c r="G39" s="26" t="n">
-        <x:v>3200</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H39" s="23" t="str"/>
       <x:c r="I39" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J39" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K39" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L39" s="23" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="23" t="str">
+        <x:v>035-SRC0149</x:v>
+      </x:c>
+      <x:c r="B40" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C40" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D40" s="23" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="E40" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F40" s="23" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G40" s="26" t="n">
+        <x:v>30100</x:v>
+      </x:c>
+      <x:c r="H40" s="23" t="str"/>
+      <x:c r="I40" s="23" t="str">
         <x:v>hours</x:v>
       </x:c>
-      <x:c r="J39" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K39" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L39" s="23" t="str"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="24" t="str">
-        <x:v>035-SRC0125</x:v>
-      </x:c>
-      <x:c r="B40" s="24" t="str">
+      <x:c r="J40" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K40" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L40" s="23" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="23" t="str">
+        <x:v>035-SRC0150</x:v>
+      </x:c>
+      <x:c r="B41" s="23" t="str">
         <x:v>Monthly capacity</x:v>
       </x:c>
-      <x:c r="C40" s="24" t="str">
+      <x:c r="C41" s="23" t="str">
         <x:v>All field labor</x:v>
       </x:c>
-      <x:c r="D40" s="24" t="str">
+      <x:c r="D41" s="23" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="E41" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F41" s="23" t="str">
+        <x:v>Subcontractable hours</x:v>
+      </x:c>
+      <x:c r="G41" s="26" t="n">
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="H41" s="23" t="str"/>
+      <x:c r="I41" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J41" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K41" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L41" s="23" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="23" t="str">
+        <x:v>035-SRC0151</x:v>
+      </x:c>
+      <x:c r="B42" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C42" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D42" s="23" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="E42" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F42" s="23" t="str">
+        <x:v>Overtime limit on internal hours</x:v>
+      </x:c>
+      <x:c r="G42" s="26" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="H42" s="23" t="str"/>
+      <x:c r="I42" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J42" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K42" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L42" s="23" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="23" t="str">
+        <x:v>035-SRC0152</x:v>
+      </x:c>
+      <x:c r="B43" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C43" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D43" s="23" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="E43" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F43" s="23" t="str">
+        <x:v>Emergency overtime increment limit</x:v>
+      </x:c>
+      <x:c r="G43" s="26" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H43" s="23" t="str"/>
+      <x:c r="I43" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J43" s="23" t="str">
+        <x:v>Approved capacity-response policy</x:v>
+      </x:c>
+      <x:c r="K43" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L43" s="23" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="23" t="str">
+        <x:v>035-SRC0153</x:v>
+      </x:c>
+      <x:c r="B44" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C44" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D44" s="23" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="E44" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F44" s="23" t="str">
+        <x:v>Contingent subcontract surge hours</x:v>
+      </x:c>
+      <x:c r="G44" s="26" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="H44" s="23" t="str"/>
+      <x:c r="I44" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J44" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K44" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L44" s="23" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="23" t="str">
+        <x:v>035-SRC0154</x:v>
+      </x:c>
+      <x:c r="B45" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C45" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D45" s="23" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="E45" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F45" s="23" t="str">
+        <x:v>Overtime premium cost</x:v>
+      </x:c>
+      <x:c r="G45" s="26" t="n">
+        <x:v>42.5</x:v>
+      </x:c>
+      <x:c r="H45" s="23" t="str"/>
+      <x:c r="I45" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J45" s="23" t="str">
+        <x:v>Approved labor-cost assumptions</x:v>
+      </x:c>
+      <x:c r="K45" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L45" s="23" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="23" t="str">
+        <x:v>035-SRC0155</x:v>
+      </x:c>
+      <x:c r="B46" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C46" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D46" s="23" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="E46" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F46" s="23" t="str">
+        <x:v>Contingent subcontract cost</x:v>
+      </x:c>
+      <x:c r="G46" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H46" s="23" t="str"/>
+      <x:c r="I46" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J46" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K46" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L46" s="23" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="23" t="str">
+        <x:v>035-SRC0156</x:v>
+      </x:c>
+      <x:c r="B47" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C47" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D47" s="23" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="E47" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F47" s="23" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G47" s="26" t="n">
+        <x:v>30380</x:v>
+      </x:c>
+      <x:c r="H47" s="23" t="str"/>
+      <x:c r="I47" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J47" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K47" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L47" s="23" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="23" t="str">
+        <x:v>035-SRC0157</x:v>
+      </x:c>
+      <x:c r="B48" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C48" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D48" s="23" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="E48" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F48" s="23" t="str">
+        <x:v>Subcontractable hours</x:v>
+      </x:c>
+      <x:c r="G48" s="26" t="n">
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="H48" s="23" t="str"/>
+      <x:c r="I48" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J48" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K48" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L48" s="23" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="23" t="str">
+        <x:v>035-SRC0158</x:v>
+      </x:c>
+      <x:c r="B49" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C49" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D49" s="23" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="E49" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F49" s="23" t="str">
+        <x:v>Overtime limit on internal hours</x:v>
+      </x:c>
+      <x:c r="G49" s="26" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="H49" s="23" t="str"/>
+      <x:c r="I49" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J49" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K49" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L49" s="23" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="23" t="str">
+        <x:v>035-SRC0159</x:v>
+      </x:c>
+      <x:c r="B50" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C50" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D50" s="23" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="E50" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F50" s="23" t="str">
+        <x:v>Emergency overtime increment limit</x:v>
+      </x:c>
+      <x:c r="G50" s="26" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H50" s="23" t="str"/>
+      <x:c r="I50" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J50" s="23" t="str">
+        <x:v>Approved capacity-response policy</x:v>
+      </x:c>
+      <x:c r="K50" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L50" s="23" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="23" t="str">
+        <x:v>035-SRC0160</x:v>
+      </x:c>
+      <x:c r="B51" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C51" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D51" s="23" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="E51" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F51" s="23" t="str">
+        <x:v>Contingent subcontract surge hours</x:v>
+      </x:c>
+      <x:c r="G51" s="26" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="H51" s="23" t="str"/>
+      <x:c r="I51" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J51" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K51" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L51" s="23" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="23" t="str">
+        <x:v>035-SRC0161</x:v>
+      </x:c>
+      <x:c r="B52" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C52" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D52" s="23" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="E52" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F52" s="23" t="str">
+        <x:v>Overtime premium cost</x:v>
+      </x:c>
+      <x:c r="G52" s="26" t="n">
+        <x:v>42.5</x:v>
+      </x:c>
+      <x:c r="H52" s="23" t="str"/>
+      <x:c r="I52" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J52" s="23" t="str">
+        <x:v>Approved labor-cost assumptions</x:v>
+      </x:c>
+      <x:c r="K52" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L52" s="23" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="23" t="str">
+        <x:v>035-SRC0162</x:v>
+      </x:c>
+      <x:c r="B53" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C53" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D53" s="23" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="E53" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F53" s="23" t="str">
+        <x:v>Contingent subcontract cost</x:v>
+      </x:c>
+      <x:c r="G53" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H53" s="23" t="str"/>
+      <x:c r="I53" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J53" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K53" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L53" s="23" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="23" t="str">
+        <x:v>035-SRC0163</x:v>
+      </x:c>
+      <x:c r="B54" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C54" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D54" s="23" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="E54" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F54" s="23" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G54" s="26" t="n">
+        <x:v>33460</x:v>
+      </x:c>
+      <x:c r="H54" s="23" t="str"/>
+      <x:c r="I54" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J54" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K54" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L54" s="23" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="23" t="str">
+        <x:v>035-SRC0164</x:v>
+      </x:c>
+      <x:c r="B55" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C55" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D55" s="23" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="E55" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F55" s="23" t="str">
+        <x:v>Subcontractable hours</x:v>
+      </x:c>
+      <x:c r="G55" s="26" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="H55" s="23" t="str"/>
+      <x:c r="I55" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J55" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K55" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L55" s="23" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="23" t="str">
+        <x:v>035-SRC0165</x:v>
+      </x:c>
+      <x:c r="B56" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C56" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D56" s="23" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="E56" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F56" s="23" t="str">
+        <x:v>Overtime limit on internal hours</x:v>
+      </x:c>
+      <x:c r="G56" s="26" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="H56" s="23" t="str"/>
+      <x:c r="I56" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J56" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K56" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L56" s="23" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="23" t="str">
+        <x:v>035-SRC0166</x:v>
+      </x:c>
+      <x:c r="B57" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C57" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D57" s="23" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="E57" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F57" s="23" t="str">
+        <x:v>Emergency overtime increment limit</x:v>
+      </x:c>
+      <x:c r="G57" s="26" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H57" s="23" t="str"/>
+      <x:c r="I57" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J57" s="23" t="str">
+        <x:v>Approved capacity-response policy</x:v>
+      </x:c>
+      <x:c r="K57" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L57" s="23" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="23" t="str">
+        <x:v>035-SRC0167</x:v>
+      </x:c>
+      <x:c r="B58" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C58" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D58" s="23" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="E58" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F58" s="23" t="str">
+        <x:v>Contingent subcontract surge hours</x:v>
+      </x:c>
+      <x:c r="G58" s="26" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H58" s="23" t="str"/>
+      <x:c r="I58" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J58" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K58" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L58" s="23" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="23" t="str">
+        <x:v>035-SRC0168</x:v>
+      </x:c>
+      <x:c r="B59" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C59" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D59" s="23" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="E59" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F59" s="23" t="str">
+        <x:v>Overtime premium cost</x:v>
+      </x:c>
+      <x:c r="G59" s="26" t="n">
+        <x:v>42.5</x:v>
+      </x:c>
+      <x:c r="H59" s="23" t="str"/>
+      <x:c r="I59" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J59" s="23" t="str">
+        <x:v>Approved labor-cost assumptions</x:v>
+      </x:c>
+      <x:c r="K59" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L59" s="23" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="23" t="str">
+        <x:v>035-SRC0169</x:v>
+      </x:c>
+      <x:c r="B60" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C60" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D60" s="23" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="E60" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F60" s="23" t="str">
+        <x:v>Contingent subcontract cost</x:v>
+      </x:c>
+      <x:c r="G60" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H60" s="23" t="str"/>
+      <x:c r="I60" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J60" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K60" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L60" s="23" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="23" t="str">
+        <x:v>035-SRC0170</x:v>
+      </x:c>
+      <x:c r="B61" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C61" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D61" s="23" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="E61" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F61" s="23" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G61" s="26" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="H61" s="23" t="str"/>
+      <x:c r="I61" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J61" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K61" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L61" s="23" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="23" t="str">
+        <x:v>035-SRC0171</x:v>
+      </x:c>
+      <x:c r="B62" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C62" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D62" s="23" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="E62" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F62" s="23" t="str">
+        <x:v>Subcontractable hours</x:v>
+      </x:c>
+      <x:c r="G62" s="26" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="H62" s="23" t="str"/>
+      <x:c r="I62" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J62" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K62" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L62" s="23" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="23" t="str">
+        <x:v>035-SRC0172</x:v>
+      </x:c>
+      <x:c r="B63" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C63" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D63" s="23" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="E63" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F63" s="23" t="str">
+        <x:v>Overtime limit on internal hours</x:v>
+      </x:c>
+      <x:c r="G63" s="26" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="H63" s="23" t="str"/>
+      <x:c r="I63" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J63" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K63" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L63" s="23" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="23" t="str">
+        <x:v>035-SRC0173</x:v>
+      </x:c>
+      <x:c r="B64" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C64" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D64" s="23" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="E64" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F64" s="23" t="str">
+        <x:v>Emergency overtime increment limit</x:v>
+      </x:c>
+      <x:c r="G64" s="26" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H64" s="23" t="str"/>
+      <x:c r="I64" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J64" s="23" t="str">
+        <x:v>Approved capacity-response policy</x:v>
+      </x:c>
+      <x:c r="K64" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L64" s="23" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="23" t="str">
+        <x:v>035-SRC0174</x:v>
+      </x:c>
+      <x:c r="B65" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C65" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D65" s="23" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="E65" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F65" s="23" t="str">
+        <x:v>Contingent subcontract surge hours</x:v>
+      </x:c>
+      <x:c r="G65" s="26" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H65" s="23" t="str"/>
+      <x:c r="I65" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J65" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K65" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L65" s="23" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="23" t="str">
+        <x:v>035-SRC0175</x:v>
+      </x:c>
+      <x:c r="B66" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C66" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D66" s="23" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="E66" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F66" s="23" t="str">
+        <x:v>Overtime premium cost</x:v>
+      </x:c>
+      <x:c r="G66" s="26" t="n">
+        <x:v>42.5</x:v>
+      </x:c>
+      <x:c r="H66" s="23" t="str"/>
+      <x:c r="I66" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J66" s="23" t="str">
+        <x:v>Approved labor-cost assumptions</x:v>
+      </x:c>
+      <x:c r="K66" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L66" s="23" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="23" t="str">
+        <x:v>035-SRC0176</x:v>
+      </x:c>
+      <x:c r="B67" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C67" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D67" s="23" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="E67" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F67" s="23" t="str">
+        <x:v>Contingent subcontract cost</x:v>
+      </x:c>
+      <x:c r="G67" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H67" s="23" t="str"/>
+      <x:c r="I67" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J67" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K67" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L67" s="23" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="23" t="str">
+        <x:v>035-SRC0177</x:v>
+      </x:c>
+      <x:c r="B68" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C68" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D68" s="23" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="E68" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F68" s="23" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G68" s="26" t="n">
+        <x:v>34020</x:v>
+      </x:c>
+      <x:c r="H68" s="23" t="str"/>
+      <x:c r="I68" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J68" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K68" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L68" s="23" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="23" t="str">
+        <x:v>035-SRC0178</x:v>
+      </x:c>
+      <x:c r="B69" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C69" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D69" s="23" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="E69" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F69" s="23" t="str">
+        <x:v>Subcontractable hours</x:v>
+      </x:c>
+      <x:c r="G69" s="26" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="H69" s="23" t="str"/>
+      <x:c r="I69" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J69" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K69" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L69" s="23" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="23" t="str">
+        <x:v>035-SRC0179</x:v>
+      </x:c>
+      <x:c r="B70" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C70" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D70" s="23" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="E70" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F70" s="23" t="str">
+        <x:v>Overtime limit on internal hours</x:v>
+      </x:c>
+      <x:c r="G70" s="26" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="H70" s="23" t="str"/>
+      <x:c r="I70" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J70" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K70" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L70" s="23" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="23" t="str">
+        <x:v>035-SRC0180</x:v>
+      </x:c>
+      <x:c r="B71" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C71" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D71" s="23" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="E71" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F71" s="23" t="str">
+        <x:v>Emergency overtime increment limit</x:v>
+      </x:c>
+      <x:c r="G71" s="26" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H71" s="23" t="str"/>
+      <x:c r="I71" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J71" s="23" t="str">
+        <x:v>Approved capacity-response policy</x:v>
+      </x:c>
+      <x:c r="K71" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L71" s="23" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="23" t="str">
+        <x:v>035-SRC0181</x:v>
+      </x:c>
+      <x:c r="B72" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C72" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D72" s="23" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="E72" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F72" s="23" t="str">
+        <x:v>Contingent subcontract surge hours</x:v>
+      </x:c>
+      <x:c r="G72" s="26" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H72" s="23" t="str"/>
+      <x:c r="I72" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J72" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K72" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L72" s="23" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="23" t="str">
+        <x:v>035-SRC0182</x:v>
+      </x:c>
+      <x:c r="B73" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C73" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D73" s="23" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="E73" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F73" s="23" t="str">
+        <x:v>Overtime premium cost</x:v>
+      </x:c>
+      <x:c r="G73" s="26" t="n">
+        <x:v>42.5</x:v>
+      </x:c>
+      <x:c r="H73" s="23" t="str"/>
+      <x:c r="I73" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J73" s="23" t="str">
+        <x:v>Approved labor-cost assumptions</x:v>
+      </x:c>
+      <x:c r="K73" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L73" s="23" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="23" t="str">
+        <x:v>035-SRC0183</x:v>
+      </x:c>
+      <x:c r="B74" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C74" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D74" s="23" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="E74" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F74" s="23" t="str">
+        <x:v>Contingent subcontract cost</x:v>
+      </x:c>
+      <x:c r="G74" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H74" s="23" t="str"/>
+      <x:c r="I74" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J74" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K74" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L74" s="23" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="23" t="str">
+        <x:v>035-SRC0184</x:v>
+      </x:c>
+      <x:c r="B75" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C75" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D75" s="23" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="E75" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F75" s="23" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G75" s="26" t="n">
+        <x:v>34300</x:v>
+      </x:c>
+      <x:c r="H75" s="23" t="str"/>
+      <x:c r="I75" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J75" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K75" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L75" s="23" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="23" t="str">
+        <x:v>035-SRC0185</x:v>
+      </x:c>
+      <x:c r="B76" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C76" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D76" s="23" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="E76" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F76" s="23" t="str">
+        <x:v>Subcontractable hours</x:v>
+      </x:c>
+      <x:c r="G76" s="26" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="H76" s="23" t="str"/>
+      <x:c r="I76" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J76" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K76" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L76" s="23" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="23" t="str">
+        <x:v>035-SRC0186</x:v>
+      </x:c>
+      <x:c r="B77" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C77" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D77" s="23" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="E77" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F77" s="23" t="str">
+        <x:v>Overtime limit on internal hours</x:v>
+      </x:c>
+      <x:c r="G77" s="26" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="H77" s="23" t="str"/>
+      <x:c r="I77" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J77" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K77" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L77" s="23" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="23" t="str">
+        <x:v>035-SRC0187</x:v>
+      </x:c>
+      <x:c r="B78" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C78" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D78" s="23" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="E78" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F78" s="23" t="str">
+        <x:v>Emergency overtime increment limit</x:v>
+      </x:c>
+      <x:c r="G78" s="26" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H78" s="23" t="str"/>
+      <x:c r="I78" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J78" s="23" t="str">
+        <x:v>Approved capacity-response policy</x:v>
+      </x:c>
+      <x:c r="K78" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L78" s="23" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="23" t="str">
+        <x:v>035-SRC0188</x:v>
+      </x:c>
+      <x:c r="B79" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C79" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D79" s="23" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="E79" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F79" s="23" t="str">
+        <x:v>Contingent subcontract surge hours</x:v>
+      </x:c>
+      <x:c r="G79" s="26" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H79" s="23" t="str"/>
+      <x:c r="I79" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J79" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K79" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L79" s="23" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="23" t="str">
+        <x:v>035-SRC0189</x:v>
+      </x:c>
+      <x:c r="B80" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C80" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D80" s="23" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="E80" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F80" s="23" t="str">
+        <x:v>Overtime premium cost</x:v>
+      </x:c>
+      <x:c r="G80" s="26" t="n">
+        <x:v>42.5</x:v>
+      </x:c>
+      <x:c r="H80" s="23" t="str"/>
+      <x:c r="I80" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J80" s="23" t="str">
+        <x:v>Approved labor-cost assumptions</x:v>
+      </x:c>
+      <x:c r="K80" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L80" s="23" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="23" t="str">
+        <x:v>035-SRC0190</x:v>
+      </x:c>
+      <x:c r="B81" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C81" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D81" s="23" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="E81" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F81" s="23" t="str">
+        <x:v>Contingent subcontract cost</x:v>
+      </x:c>
+      <x:c r="G81" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H81" s="23" t="str"/>
+      <x:c r="I81" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J81" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K81" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L81" s="23" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="23" t="str">
+        <x:v>035-SRC0191</x:v>
+      </x:c>
+      <x:c r="B82" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C82" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D82" s="23" t="str">
         <x:v>2027-06</x:v>
       </x:c>
-      <x:c r="E40" s="24" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F40" s="24" t="str">
+      <x:c r="E82" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F82" s="23" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="G82" s="26" t="n">
+        <x:v>34580</x:v>
+      </x:c>
+      <x:c r="H82" s="23" t="str"/>
+      <x:c r="I82" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J82" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K82" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L82" s="23" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="23" t="str">
+        <x:v>035-SRC0192</x:v>
+      </x:c>
+      <x:c r="B83" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C83" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D83" s="23" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="E83" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F83" s="23" t="str">
+        <x:v>Subcontractable hours</x:v>
+      </x:c>
+      <x:c r="G83" s="26" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="H83" s="23" t="str"/>
+      <x:c r="I83" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J83" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K83" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L83" s="23" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="23" t="str">
+        <x:v>035-SRC0193</x:v>
+      </x:c>
+      <x:c r="B84" s="23" t="str">
+        <x:v>Monthly capacity</x:v>
+      </x:c>
+      <x:c r="C84" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D84" s="23" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="E84" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F84" s="23" t="str">
         <x:v>Overtime limit on internal hours</x:v>
       </x:c>
-      <x:c r="G40" s="27" t="n">
+      <x:c r="G84" s="26" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="H40" s="24" t="str"/>
-      <x:c r="I40" s="24" t="str">
-        <x:v>decimal ratio</x:v>
-      </x:c>
-      <x:c r="J40" s="24" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K40" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L40" s="24" t="str"/>
+      <x:c r="H84" s="23" t="str"/>
+      <x:c r="I84" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J84" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K84" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L84" s="23" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="23" t="str">
+        <x:v>035-SRC0194</x:v>
+      </x:c>
+      <x:c r="B85" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C85" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D85" s="23" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="E85" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F85" s="23" t="str">
+        <x:v>Emergency overtime increment limit</x:v>
+      </x:c>
+      <x:c r="G85" s="26" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H85" s="23" t="str"/>
+      <x:c r="I85" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J85" s="23" t="str">
+        <x:v>Approved capacity-response policy</x:v>
+      </x:c>
+      <x:c r="K85" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L85" s="23" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="23" t="str">
+        <x:v>035-SRC0195</x:v>
+      </x:c>
+      <x:c r="B86" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C86" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D86" s="23" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="E86" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F86" s="23" t="str">
+        <x:v>Contingent subcontract surge hours</x:v>
+      </x:c>
+      <x:c r="G86" s="26" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H86" s="23" t="str"/>
+      <x:c r="I86" s="23" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="J86" s="23" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K86" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L86" s="23" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="23" t="str">
+        <x:v>035-SRC0196</x:v>
+      </x:c>
+      <x:c r="B87" s="23" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C87" s="23" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D87" s="23" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="E87" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F87" s="23" t="str">
+        <x:v>Overtime premium cost</x:v>
+      </x:c>
+      <x:c r="G87" s="26" t="n">
+        <x:v>42.5</x:v>
+      </x:c>
+      <x:c r="H87" s="23" t="str"/>
+      <x:c r="I87" s="23" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J87" s="23" t="str">
+        <x:v>Approved labor-cost assumptions</x:v>
+      </x:c>
+      <x:c r="K87" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L87" s="23" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="24" t="str">
+        <x:v>035-SRC0197</x:v>
+      </x:c>
+      <x:c r="B88" s="24" t="str">
+        <x:v>Capacity remediation</x:v>
+      </x:c>
+      <x:c r="C88" s="24" t="str">
+        <x:v>All field labor</x:v>
+      </x:c>
+      <x:c r="D88" s="24" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="E88" s="24" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F88" s="24" t="str">
+        <x:v>Contingent subcontract cost</x:v>
+      </x:c>
+      <x:c r="G88" s="27" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H88" s="24" t="str"/>
+      <x:c r="I88" s="24" t="str">
+        <x:v>USD per hour</x:v>
+      </x:c>
+      <x:c r="J88" s="24" t="str">
+        <x:v>Executed contingent labor framework</x:v>
+      </x:c>
+      <x:c r="K88" s="30" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L88" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4900,19 +6564,23 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Revenue Burn</x:v>
+        <x:v>Complete the backlog burn and capacity model | Execution Authority</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -4921,10 +6589,14 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
+      <x:c r="L1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>LOCKED INPUT SCHEDULE • refreshed from current management workbooks and Vista ERP • Do not edit</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -4933,189 +6605,869 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
+      <x:c r="K2" s="6"/>
+      <x:c r="L2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Source Ref</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Schedule</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Entity</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Period</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Scenario</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Measure</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Numeric Value</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Text Value</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
+        <x:v>Source Document</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="str">
+        <x:v>Source Date</x:v>
+      </x:c>
+      <x:c r="L4" s="17" t="str">
+        <x:v>System Tie</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>signed_backlog</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="22" t="str">
+        <x:v>035-SRC0005</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G5" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="22" t="str"/>
+      <x:c r="I5" s="22" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J5" s="22" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K5" s="28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L5" s="22" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>fy27_backlog_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="23" t="str">
+        <x:v>035-SRC0006</x:v>
+      </x:c>
+      <x:c r="B6" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C6" s="23" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="D6" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E6" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F6" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G6" s="26" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="H6" s="23" t="str"/>
+      <x:c r="I6" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J6" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K6" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L6" s="23" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>first_constrained_month</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="23" t="str">
+        <x:v>035-SRC0007</x:v>
+      </x:c>
+      <x:c r="B7" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C7" s="23" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="D7" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E7" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F7" s="23" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="n">
+        <x:v>0.006</x:v>
+      </x:c>
+      <x:c r="H7" s="23" t="str"/>
+      <x:c r="I7" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J7" s="23" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K7" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L7" s="23" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="34" t="str">
-        <x:v>maximum_capacity_shortfall_hours</x:v>
-      </x:c>
-      <x:c r="B8" s="37"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
+      <x:c r="A8" s="23" t="str">
+        <x:v>035-SRC0024</x:v>
+      </x:c>
+      <x:c r="B8" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C8" s="23" t="str">
+        <x:v>P-3107</x:v>
+      </x:c>
+      <x:c r="D8" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E8" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F8" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G8" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H8" s="23" t="str"/>
+      <x:c r="I8" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J8" s="23" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K8" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L8" s="23" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="23" t="str">
+        <x:v>035-SRC0025</x:v>
+      </x:c>
+      <x:c r="B9" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C9" s="23" t="str">
+        <x:v>P-3107</x:v>
+      </x:c>
+      <x:c r="D9" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E9" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F9" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G9" s="26" t="n">
+        <x:v>0.22</x:v>
+      </x:c>
+      <x:c r="H9" s="23" t="str"/>
+      <x:c r="I9" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J9" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K9" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L9" s="23" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="23" t="str">
+        <x:v>035-SRC0026</x:v>
+      </x:c>
+      <x:c r="B10" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C10" s="23" t="str">
+        <x:v>P-3107</x:v>
+      </x:c>
+      <x:c r="D10" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E10" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F10" s="23" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G10" s="26" t="n">
+        <x:v>0.008</x:v>
+      </x:c>
+      <x:c r="H10" s="23" t="str"/>
+      <x:c r="I10" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J10" s="23" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K10" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L10" s="23" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="23" t="str">
+        <x:v>035-SRC0042</x:v>
+      </x:c>
+      <x:c r="B11" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="D11" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F11" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G11" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="23" t="str"/>
+      <x:c r="I11" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J11" s="23" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K11" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L11" s="23" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="40"/>
-      <x:c r="B12" s="40"/>
-      <x:c r="C12" s="40"/>
-      <x:c r="D12" s="40"/>
-      <x:c r="E12" s="40"/>
-      <x:c r="F12" s="40"/>
-      <x:c r="G12" s="40"/>
-      <x:c r="H12" s="40"/>
+      <x:c r="A12" s="23" t="str">
+        <x:v>035-SRC0043</x:v>
+      </x:c>
+      <x:c r="B12" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G12" s="26" t="n">
+        <x:v>0.27</x:v>
+      </x:c>
+      <x:c r="H12" s="23" t="str"/>
+      <x:c r="I12" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J12" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K12" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L12" s="23" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="41"/>
-      <x:c r="B13" s="41"/>
-      <x:c r="C13" s="41"/>
-      <x:c r="D13" s="41"/>
-      <x:c r="E13" s="41"/>
-      <x:c r="F13" s="41"/>
-      <x:c r="G13" s="41"/>
-      <x:c r="H13" s="41"/>
+      <x:c r="A13" s="23" t="str">
+        <x:v>035-SRC0044</x:v>
+      </x:c>
+      <x:c r="B13" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G13" s="26" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="H13" s="23" t="str"/>
+      <x:c r="I13" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J13" s="23" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K13" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L13" s="23" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="41"/>
-      <x:c r="B14" s="41"/>
-      <x:c r="C14" s="41"/>
-      <x:c r="D14" s="41"/>
-      <x:c r="E14" s="41"/>
-      <x:c r="F14" s="41"/>
-      <x:c r="G14" s="41"/>
-      <x:c r="H14" s="41"/>
+      <x:c r="A14" s="23" t="str">
+        <x:v>035-SRC0058</x:v>
+      </x:c>
+      <x:c r="B14" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="str">
+        <x:v>P-3122</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F14" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G14" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="23" t="str"/>
+      <x:c r="I14" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J14" s="23" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K14" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L14" s="23" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="41"/>
-      <x:c r="B15" s="41"/>
-      <x:c r="C15" s="41"/>
-      <x:c r="D15" s="41"/>
-      <x:c r="E15" s="41"/>
-      <x:c r="F15" s="41"/>
-      <x:c r="G15" s="41"/>
-      <x:c r="H15" s="41"/>
+      <x:c r="A15" s="23" t="str">
+        <x:v>035-SRC0059</x:v>
+      </x:c>
+      <x:c r="B15" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="str">
+        <x:v>P-3122</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F15" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G15" s="26" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H15" s="23" t="str"/>
+      <x:c r="I15" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J15" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K15" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L15" s="23" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="41"/>
-      <x:c r="B16" s="41"/>
-      <x:c r="C16" s="41"/>
-      <x:c r="D16" s="41"/>
-      <x:c r="E16" s="41"/>
-      <x:c r="F16" s="41"/>
-      <x:c r="G16" s="41"/>
-      <x:c r="H16" s="41"/>
+      <x:c r="A16" s="23" t="str">
+        <x:v>035-SRC0060</x:v>
+      </x:c>
+      <x:c r="B16" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="str">
+        <x:v>P-3122</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F16" s="23" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G16" s="26" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="H16" s="23" t="str"/>
+      <x:c r="I16" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J16" s="23" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K16" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L16" s="23" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
+      <x:c r="A17" s="23" t="str">
+        <x:v>035-SRC0072</x:v>
+      </x:c>
+      <x:c r="B17" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="str">
+        <x:v>P-3130</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F17" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G17" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H17" s="23" t="str"/>
+      <x:c r="I17" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J17" s="23" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K17" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L17" s="23" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
+      <x:c r="A18" s="23" t="str">
+        <x:v>035-SRC0073</x:v>
+      </x:c>
+      <x:c r="B18" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="str">
+        <x:v>P-3130</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F18" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G18" s="26" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="H18" s="23" t="str"/>
+      <x:c r="I18" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J18" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K18" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L18" s="23" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="41"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="41"/>
-      <x:c r="E19" s="41"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="41"/>
-      <x:c r="H19" s="41"/>
+      <x:c r="A19" s="23" t="str">
+        <x:v>035-SRC0074</x:v>
+      </x:c>
+      <x:c r="B19" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="str">
+        <x:v>P-3130</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F19" s="23" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G19" s="26" t="n">
+        <x:v>0.009</x:v>
+      </x:c>
+      <x:c r="H19" s="23" t="str"/>
+      <x:c r="I19" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J19" s="23" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K19" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L19" s="23" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="41"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="41"/>
-      <x:c r="E20" s="41"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="41"/>
-      <x:c r="H20" s="41"/>
+      <x:c r="A20" s="23" t="str">
+        <x:v>035-SRC0085</x:v>
+      </x:c>
+      <x:c r="B20" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="str">
+        <x:v>P-3138</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F20" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G20" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H20" s="23" t="str"/>
+      <x:c r="I20" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J20" s="23" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K20" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L20" s="23" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="41"/>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
+      <x:c r="A21" s="23" t="str">
+        <x:v>035-SRC0086</x:v>
+      </x:c>
+      <x:c r="B21" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="str">
+        <x:v>P-3138</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G21" s="26" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="H21" s="23" t="str"/>
+      <x:c r="I21" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J21" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K21" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L21" s="23" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="41"/>
-      <x:c r="B22" s="41"/>
-      <x:c r="C22" s="41"/>
-      <x:c r="D22" s="41"/>
-      <x:c r="E22" s="41"/>
-      <x:c r="F22" s="41"/>
-      <x:c r="G22" s="41"/>
-      <x:c r="H22" s="41"/>
+      <x:c r="A22" s="23" t="str">
+        <x:v>035-SRC0087</x:v>
+      </x:c>
+      <x:c r="B22" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="str">
+        <x:v>P-3138</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F22" s="23" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G22" s="26" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="H22" s="23" t="str"/>
+      <x:c r="I22" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J22" s="23" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K22" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L22" s="23" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="42"/>
-      <x:c r="B23" s="42"/>
-      <x:c r="C23" s="42"/>
-      <x:c r="D23" s="42"/>
-      <x:c r="E23" s="42"/>
-      <x:c r="F23" s="42"/>
-      <x:c r="G23" s="42"/>
-      <x:c r="H23" s="42"/>
+      <x:c r="A23" s="23" t="str">
+        <x:v>035-SRC0097</x:v>
+      </x:c>
+      <x:c r="B23" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="str">
+        <x:v>P-3145</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E23" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F23" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G23" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H23" s="23" t="str"/>
+      <x:c r="I23" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J23" s="23" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K23" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L23" s="23" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23" t="str">
+        <x:v>035-SRC0098</x:v>
+      </x:c>
+      <x:c r="B24" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="str">
+        <x:v>P-3145</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E24" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F24" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G24" s="26" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="H24" s="23" t="str"/>
+      <x:c r="I24" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J24" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K24" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L24" s="23" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="23" t="str">
+        <x:v>035-SRC0099</x:v>
+      </x:c>
+      <x:c r="B25" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C25" s="23" t="str">
+        <x:v>P-3145</x:v>
+      </x:c>
+      <x:c r="D25" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E25" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F25" s="23" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G25" s="26" t="n">
+        <x:v>0.011</x:v>
+      </x:c>
+      <x:c r="H25" s="23" t="str"/>
+      <x:c r="I25" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J25" s="23" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K25" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L25" s="23" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23" t="str">
+        <x:v>035-SRC0108</x:v>
+      </x:c>
+      <x:c r="B26" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="str">
+        <x:v>P-3152</x:v>
+      </x:c>
+      <x:c r="D26" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E26" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F26" s="23" t="str">
+        <x:v>Customer delivery priority</x:v>
+      </x:c>
+      <x:c r="G26" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H26" s="23" t="str"/>
+      <x:c r="I26" s="23" t="str">
+        <x:v>priority rank</x:v>
+      </x:c>
+      <x:c r="J26" s="23" t="str">
+        <x:v>Approved project-execution register</x:v>
+      </x:c>
+      <x:c r="K26" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L26" s="23" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="23" t="str">
+        <x:v>035-SRC0109</x:v>
+      </x:c>
+      <x:c r="B27" s="23" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="str">
+        <x:v>P-3152</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E27" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F27" s="23" t="str">
+        <x:v>Contract gross margin</x:v>
+      </x:c>
+      <x:c r="G27" s="26" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="H27" s="23" t="str"/>
+      <x:c r="I27" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J27" s="23" t="str">
+        <x:v>Controller-approved project economics</x:v>
+      </x:c>
+      <x:c r="K27" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L27" s="23" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="24" t="str">
+        <x:v>035-SRC0110</x:v>
+      </x:c>
+      <x:c r="B28" s="24" t="str">
+        <x:v>Execution authority</x:v>
+      </x:c>
+      <x:c r="C28" s="24" t="str">
+        <x:v>P-3152</x:v>
+      </x:c>
+      <x:c r="D28" s="24" t="str">
+        <x:v>FY27</x:v>
+      </x:c>
+      <x:c r="E28" s="24" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F28" s="24" t="str">
+        <x:v>Monthly liquidated damages rate</x:v>
+      </x:c>
+      <x:c r="G28" s="27" t="n">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="H28" s="24" t="str"/>
+      <x:c r="I28" s="24" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J28" s="24" t="str">
+        <x:v>Executed contract terms</x:v>
+      </x:c>
+      <x:c r="K28" s="30" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L28" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5125,19 +7477,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Labor Capacity</x:v>
+        <x:v>FY27 backlog burn | planning cases</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -5149,7 +7501,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>Build from the controlled source schedules; keep probability plan, signed commitment, and pipeline distinct</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -5161,181 +7513,223 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Case</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Signed backlog</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>FY27 revenue</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Required hours</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>First constrained month</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Unresolved hours</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Remediation cost</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="str">
+        <x:v>Release conclusion</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>signed_backlog</x:v>
+      <x:c r="A5" s="35" t="str">
+        <x:v>Approved probability plan</x:v>
       </x:c>
       <x:c r="B5" s="35"/>
+      <x:c r="C5" s="35"/>
+      <x:c r="D5" s="35"/>
+      <x:c r="E5" s="35"/>
+      <x:c r="F5" s="35"/>
+      <x:c r="G5" s="35"/>
+      <x:c r="H5" s="35"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>fy27_backlog_revenue_burn</x:v>
+      <x:c r="A6" s="36" t="str">
+        <x:v>Full signed commitment</x:v>
       </x:c>
       <x:c r="B6" s="36"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>first_constrained_month</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="34" t="str">
-        <x:v>maximum_capacity_shortfall_hours</x:v>
-      </x:c>
-      <x:c r="B8" s="37"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
+      <x:c r="C6" s="36"/>
+      <x:c r="D6" s="36"/>
+      <x:c r="E6" s="36"/>
+      <x:c r="F6" s="36"/>
+      <x:c r="G6" s="36"/>
+      <x:c r="H6" s="36"/>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="15" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>Probability-plan revenue</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>Gross-commitment revenue</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>Revenue variance</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>Probability-plan hours</x:v>
+      </x:c>
+      <x:c r="F9" s="16" t="str">
+        <x:v>Gross-commitment hours</x:v>
+      </x:c>
+      <x:c r="G9" s="16" t="str">
+        <x:v>Source / version</x:v>
+      </x:c>
+      <x:c r="H9" s="17" t="str">
+        <x:v>Control</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B10" s="45"/>
+      <x:c r="C10" s="45"/>
+      <x:c r="D10" s="45"/>
+      <x:c r="E10" s="45"/>
+      <x:c r="F10" s="45"/>
+      <x:c r="G10" s="45"/>
+      <x:c r="H10" s="45"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="B11" s="46"/>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="40"/>
-      <x:c r="B12" s="40"/>
-      <x:c r="C12" s="40"/>
-      <x:c r="D12" s="40"/>
-      <x:c r="E12" s="40"/>
-      <x:c r="F12" s="40"/>
-      <x:c r="G12" s="40"/>
-      <x:c r="H12" s="40"/>
+      <x:c r="A12" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B12" s="46"/>
+      <x:c r="C12" s="46"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="46"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="41"/>
-      <x:c r="B13" s="41"/>
-      <x:c r="C13" s="41"/>
-      <x:c r="D13" s="41"/>
-      <x:c r="E13" s="41"/>
-      <x:c r="F13" s="41"/>
-      <x:c r="G13" s="41"/>
-      <x:c r="H13" s="41"/>
+      <x:c r="A13" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="B13" s="46"/>
+      <x:c r="C13" s="46"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="46"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="41"/>
-      <x:c r="B14" s="41"/>
-      <x:c r="C14" s="41"/>
-      <x:c r="D14" s="41"/>
-      <x:c r="E14" s="41"/>
-      <x:c r="F14" s="41"/>
-      <x:c r="G14" s="41"/>
-      <x:c r="H14" s="41"/>
+      <x:c r="A14" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="B14" s="46"/>
+      <x:c r="C14" s="46"/>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="46"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="41"/>
-      <x:c r="B15" s="41"/>
-      <x:c r="C15" s="41"/>
-      <x:c r="D15" s="41"/>
-      <x:c r="E15" s="41"/>
-      <x:c r="F15" s="41"/>
-      <x:c r="G15" s="41"/>
-      <x:c r="H15" s="41"/>
+      <x:c r="A15" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="B15" s="46"/>
+      <x:c r="C15" s="46"/>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="46"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="41"/>
-      <x:c r="B16" s="41"/>
-      <x:c r="C16" s="41"/>
-      <x:c r="D16" s="41"/>
-      <x:c r="E16" s="41"/>
-      <x:c r="F16" s="41"/>
-      <x:c r="G16" s="41"/>
-      <x:c r="H16" s="41"/>
+      <x:c r="A16" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="B16" s="46"/>
+      <x:c r="C16" s="46"/>
+      <x:c r="D16" s="46"/>
+      <x:c r="E16" s="46"/>
+      <x:c r="F16" s="46"/>
+      <x:c r="G16" s="46"/>
+      <x:c r="H16" s="46"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
+      <x:c r="A17" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="B17" s="46"/>
+      <x:c r="C17" s="46"/>
+      <x:c r="D17" s="46"/>
+      <x:c r="E17" s="46"/>
+      <x:c r="F17" s="46"/>
+      <x:c r="G17" s="46"/>
+      <x:c r="H17" s="46"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
+      <x:c r="A18" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="B18" s="46"/>
+      <x:c r="C18" s="46"/>
+      <x:c r="D18" s="46"/>
+      <x:c r="E18" s="46"/>
+      <x:c r="F18" s="46"/>
+      <x:c r="G18" s="46"/>
+      <x:c r="H18" s="46"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="41"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="41"/>
-      <x:c r="E19" s="41"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="41"/>
-      <x:c r="H19" s="41"/>
+      <x:c r="A19" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="B19" s="46"/>
+      <x:c r="C19" s="46"/>
+      <x:c r="D19" s="46"/>
+      <x:c r="E19" s="46"/>
+      <x:c r="F19" s="46"/>
+      <x:c r="G19" s="46"/>
+      <x:c r="H19" s="46"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="41"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="41"/>
-      <x:c r="E20" s="41"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="41"/>
-      <x:c r="H20" s="41"/>
+      <x:c r="A20" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="B20" s="46"/>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="46"/>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="46"/>
+      <x:c r="G20" s="46"/>
+      <x:c r="H20" s="46"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="41"/>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="41"/>
-      <x:c r="B22" s="41"/>
-      <x:c r="C22" s="41"/>
-      <x:c r="D22" s="41"/>
-      <x:c r="E22" s="41"/>
-      <x:c r="F22" s="41"/>
-      <x:c r="G22" s="41"/>
-      <x:c r="H22" s="41"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="42"/>
-      <x:c r="B23" s="42"/>
-      <x:c r="C23" s="42"/>
-      <x:c r="D23" s="42"/>
-      <x:c r="E23" s="42"/>
-      <x:c r="F23" s="42"/>
-      <x:c r="G23" s="42"/>
-      <x:c r="H23" s="42"/>
+      <x:c r="A21" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="B21" s="47"/>
+      <x:c r="C21" s="47"/>
+      <x:c r="D21" s="47"/>
+      <x:c r="E21" s="47"/>
+      <x:c r="F21" s="47"/>
+      <x:c r="G21" s="47"/>
+      <x:c r="H21" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5350,19 +7744,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Gap Analysis</x:v>
+        <x:v>FY27 labor capacity | approved availability</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -5371,10 +7766,11 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>Reconcile recurring capacity and keep ordinary availability separate from emergency response</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -5383,189 +7779,197 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Productive internal hours</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Permitted overtime</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Planned subcontractable</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Base available hours</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Emergency OT capacity</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Contingent surge capacity</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Remediated available hours</x:v>
+      </x:c>
+      <x:c r="I4" s="17" t="str">
+        <x:v>Source / authority</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>signed_backlog</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B5" s="45"/>
+      <x:c r="C5" s="45"/>
+      <x:c r="D5" s="45"/>
+      <x:c r="E5" s="45"/>
+      <x:c r="F5" s="45"/>
+      <x:c r="G5" s="45"/>
+      <x:c r="H5" s="45"/>
+      <x:c r="I5" s="45"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>fy27_backlog_revenue_burn</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="B6" s="46"/>
+      <x:c r="C6" s="46"/>
+      <x:c r="D6" s="46"/>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
+      <x:c r="I6" s="46"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>first_constrained_month</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B7" s="46"/>
+      <x:c r="C7" s="46"/>
+      <x:c r="D7" s="46"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="46"/>
+      <x:c r="G7" s="46"/>
+      <x:c r="H7" s="46"/>
+      <x:c r="I7" s="46"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="34" t="str">
-        <x:v>maximum_capacity_shortfall_hours</x:v>
-      </x:c>
-      <x:c r="B8" s="37"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
+      <x:c r="A8" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="B8" s="46"/>
+      <x:c r="C8" s="46"/>
+      <x:c r="D8" s="46"/>
+      <x:c r="E8" s="46"/>
+      <x:c r="F8" s="46"/>
+      <x:c r="G8" s="46"/>
+      <x:c r="H8" s="46"/>
+      <x:c r="I8" s="46"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="B9" s="46"/>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="B10" s="46"/>
+      <x:c r="C10" s="46"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="46"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
+      <x:c r="I10" s="46"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="B11" s="46"/>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
+      <x:c r="I11" s="46"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="40"/>
-      <x:c r="B12" s="40"/>
-      <x:c r="C12" s="40"/>
-      <x:c r="D12" s="40"/>
-      <x:c r="E12" s="40"/>
-      <x:c r="F12" s="40"/>
-      <x:c r="G12" s="40"/>
-      <x:c r="H12" s="40"/>
+      <x:c r="A12" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="B12" s="46"/>
+      <x:c r="C12" s="46"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="46"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
+      <x:c r="I12" s="46"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="41"/>
-      <x:c r="B13" s="41"/>
-      <x:c r="C13" s="41"/>
-      <x:c r="D13" s="41"/>
-      <x:c r="E13" s="41"/>
-      <x:c r="F13" s="41"/>
-      <x:c r="G13" s="41"/>
-      <x:c r="H13" s="41"/>
+      <x:c r="A13" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="B13" s="46"/>
+      <x:c r="C13" s="46"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="46"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
+      <x:c r="I13" s="46"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="41"/>
-      <x:c r="B14" s="41"/>
-      <x:c r="C14" s="41"/>
-      <x:c r="D14" s="41"/>
-      <x:c r="E14" s="41"/>
-      <x:c r="F14" s="41"/>
-      <x:c r="G14" s="41"/>
-      <x:c r="H14" s="41"/>
+      <x:c r="A14" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="B14" s="46"/>
+      <x:c r="C14" s="46"/>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="46"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
+      <x:c r="I14" s="46"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="41"/>
-      <x:c r="B15" s="41"/>
-      <x:c r="C15" s="41"/>
-      <x:c r="D15" s="41"/>
-      <x:c r="E15" s="41"/>
-      <x:c r="F15" s="41"/>
-      <x:c r="G15" s="41"/>
-      <x:c r="H15" s="41"/>
+      <x:c r="A15" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="B15" s="46"/>
+      <x:c r="C15" s="46"/>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="46"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
+      <x:c r="I15" s="46"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="41"/>
-      <x:c r="B16" s="41"/>
-      <x:c r="C16" s="41"/>
-      <x:c r="D16" s="41"/>
-      <x:c r="E16" s="41"/>
-      <x:c r="F16" s="41"/>
-      <x:c r="G16" s="41"/>
-      <x:c r="H16" s="41"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="41"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="41"/>
-      <x:c r="E19" s="41"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="41"/>
-      <x:c r="H19" s="41"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="41"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="41"/>
-      <x:c r="E20" s="41"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="41"/>
-      <x:c r="H20" s="41"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="41"/>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="41"/>
-      <x:c r="B22" s="41"/>
-      <x:c r="C22" s="41"/>
-      <x:c r="D22" s="41"/>
-      <x:c r="E22" s="41"/>
-      <x:c r="F22" s="41"/>
-      <x:c r="G22" s="41"/>
-      <x:c r="H22" s="41"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="42"/>
-      <x:c r="B23" s="42"/>
-      <x:c r="C23" s="42"/>
-      <x:c r="D23" s="42"/>
-      <x:c r="E23" s="42"/>
-      <x:c r="F23" s="42"/>
-      <x:c r="G23" s="42"/>
-      <x:c r="H23" s="42"/>
+      <x:c r="A16" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="B16" s="47"/>
+      <x:c r="C16" s="47"/>
+      <x:c r="D16" s="47"/>
+      <x:c r="E16" s="47"/>
+      <x:c r="F16" s="47"/>
+      <x:c r="G16" s="47"/>
+      <x:c r="H16" s="47"/>
+      <x:c r="I16" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5575,18 +7979,22 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the backlog burn and capacity model | Checks</x:v>
+        <x:v>FY27 capacity response | case comparison</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -5595,10 +8003,13 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>Capacity gap = required hours less available hours; positive is a shortfall and negative is spare capacity</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -5607,6 +8018,872 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
+      <x:c r="K2" s="6"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="15" t="str">
+        <x:v>Case</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Required hours</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Available hours</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Capacity gap</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Emergency OT used</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Surge used</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>Unresolved shortfall</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
+        <x:v>Remediation cost</x:v>
+      </x:c>
+      <x:c r="K4" s="17" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="45" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B5" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="C5" s="45"/>
+      <x:c r="D5" s="45"/>
+      <x:c r="E5" s="45"/>
+      <x:c r="F5" s="45"/>
+      <x:c r="G5" s="45"/>
+      <x:c r="H5" s="45"/>
+      <x:c r="I5" s="45"/>
+      <x:c r="J5" s="45"/>
+      <x:c r="K5" s="45"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B6" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="C6" s="46"/>
+      <x:c r="D6" s="46"/>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
+      <x:c r="I6" s="46"/>
+      <x:c r="J6" s="46"/>
+      <x:c r="K6" s="46"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B7" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="C7" s="46"/>
+      <x:c r="D7" s="46"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="46"/>
+      <x:c r="G7" s="46"/>
+      <x:c r="H7" s="46"/>
+      <x:c r="I7" s="46"/>
+      <x:c r="J7" s="46"/>
+      <x:c r="K7" s="46"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B8" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="C8" s="46"/>
+      <x:c r="D8" s="46"/>
+      <x:c r="E8" s="46"/>
+      <x:c r="F8" s="46"/>
+      <x:c r="G8" s="46"/>
+      <x:c r="H8" s="46"/>
+      <x:c r="I8" s="46"/>
+      <x:c r="J8" s="46"/>
+      <x:c r="K8" s="46"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B9" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
+      <x:c r="J9" s="46"/>
+      <x:c r="K9" s="46"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B10" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="C10" s="46"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="46"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
+      <x:c r="I10" s="46"/>
+      <x:c r="J10" s="46"/>
+      <x:c r="K10" s="46"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B11" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
+      <x:c r="I11" s="46"/>
+      <x:c r="J11" s="46"/>
+      <x:c r="K11" s="46"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B12" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="C12" s="46"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="46"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
+      <x:c r="I12" s="46"/>
+      <x:c r="J12" s="46"/>
+      <x:c r="K12" s="46"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B13" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="C13" s="46"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="46"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
+      <x:c r="I13" s="46"/>
+      <x:c r="J13" s="46"/>
+      <x:c r="K13" s="46"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B14" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="C14" s="46"/>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="46"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
+      <x:c r="I14" s="46"/>
+      <x:c r="J14" s="46"/>
+      <x:c r="K14" s="46"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B15" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="C15" s="46"/>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="46"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
+      <x:c r="I15" s="46"/>
+      <x:c r="J15" s="46"/>
+      <x:c r="K15" s="46"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="46" t="str">
+        <x:v>Approved probability plan</x:v>
+      </x:c>
+      <x:c r="B16" s="46" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="C16" s="46"/>
+      <x:c r="D16" s="46"/>
+      <x:c r="E16" s="46"/>
+      <x:c r="F16" s="46"/>
+      <x:c r="G16" s="46"/>
+      <x:c r="H16" s="46"/>
+      <x:c r="I16" s="46"/>
+      <x:c r="J16" s="46"/>
+      <x:c r="K16" s="46"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B17" s="46" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="C17" s="46"/>
+      <x:c r="D17" s="46"/>
+      <x:c r="E17" s="46"/>
+      <x:c r="F17" s="46"/>
+      <x:c r="G17" s="46"/>
+      <x:c r="H17" s="46"/>
+      <x:c r="I17" s="46"/>
+      <x:c r="J17" s="46"/>
+      <x:c r="K17" s="46"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B18" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="C18" s="46"/>
+      <x:c r="D18" s="46"/>
+      <x:c r="E18" s="46"/>
+      <x:c r="F18" s="46"/>
+      <x:c r="G18" s="46"/>
+      <x:c r="H18" s="46"/>
+      <x:c r="I18" s="46"/>
+      <x:c r="J18" s="46"/>
+      <x:c r="K18" s="46"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B19" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="C19" s="46"/>
+      <x:c r="D19" s="46"/>
+      <x:c r="E19" s="46"/>
+      <x:c r="F19" s="46"/>
+      <x:c r="G19" s="46"/>
+      <x:c r="H19" s="46"/>
+      <x:c r="I19" s="46"/>
+      <x:c r="J19" s="46"/>
+      <x:c r="K19" s="46"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B20" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="46"/>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="46"/>
+      <x:c r="G20" s="46"/>
+      <x:c r="H20" s="46"/>
+      <x:c r="I20" s="46"/>
+      <x:c r="J20" s="46"/>
+      <x:c r="K20" s="46"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B21" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="C21" s="46"/>
+      <x:c r="D21" s="46"/>
+      <x:c r="E21" s="46"/>
+      <x:c r="F21" s="46"/>
+      <x:c r="G21" s="46"/>
+      <x:c r="H21" s="46"/>
+      <x:c r="I21" s="46"/>
+      <x:c r="J21" s="46"/>
+      <x:c r="K21" s="46"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B22" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="C22" s="46"/>
+      <x:c r="D22" s="46"/>
+      <x:c r="E22" s="46"/>
+      <x:c r="F22" s="46"/>
+      <x:c r="G22" s="46"/>
+      <x:c r="H22" s="46"/>
+      <x:c r="I22" s="46"/>
+      <x:c r="J22" s="46"/>
+      <x:c r="K22" s="46"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B23" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="C23" s="46"/>
+      <x:c r="D23" s="46"/>
+      <x:c r="E23" s="46"/>
+      <x:c r="F23" s="46"/>
+      <x:c r="G23" s="46"/>
+      <x:c r="H23" s="46"/>
+      <x:c r="I23" s="46"/>
+      <x:c r="J23" s="46"/>
+      <x:c r="K23" s="46"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B24" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="C24" s="46"/>
+      <x:c r="D24" s="46"/>
+      <x:c r="E24" s="46"/>
+      <x:c r="F24" s="46"/>
+      <x:c r="G24" s="46"/>
+      <x:c r="H24" s="46"/>
+      <x:c r="I24" s="46"/>
+      <x:c r="J24" s="46"/>
+      <x:c r="K24" s="46"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B25" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="C25" s="46"/>
+      <x:c r="D25" s="46"/>
+      <x:c r="E25" s="46"/>
+      <x:c r="F25" s="46"/>
+      <x:c r="G25" s="46"/>
+      <x:c r="H25" s="46"/>
+      <x:c r="I25" s="46"/>
+      <x:c r="J25" s="46"/>
+      <x:c r="K25" s="46"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B26" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="C26" s="46"/>
+      <x:c r="D26" s="46"/>
+      <x:c r="E26" s="46"/>
+      <x:c r="F26" s="46"/>
+      <x:c r="G26" s="46"/>
+      <x:c r="H26" s="46"/>
+      <x:c r="I26" s="46"/>
+      <x:c r="J26" s="46"/>
+      <x:c r="K26" s="46"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="46" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B27" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="C27" s="46"/>
+      <x:c r="D27" s="46"/>
+      <x:c r="E27" s="46"/>
+      <x:c r="F27" s="46"/>
+      <x:c r="G27" s="46"/>
+      <x:c r="H27" s="46"/>
+      <x:c r="I27" s="46"/>
+      <x:c r="J27" s="46"/>
+      <x:c r="K27" s="46"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="47" t="str">
+        <x:v>Full signed commitment</x:v>
+      </x:c>
+      <x:c r="B28" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="C28" s="47"/>
+      <x:c r="D28" s="47"/>
+      <x:c r="E28" s="47"/>
+      <x:c r="F28" s="47"/>
+      <x:c r="G28" s="47"/>
+      <x:c r="H28" s="47"/>
+      <x:c r="I28" s="47"/>
+      <x:c r="J28" s="47"/>
+      <x:c r="K28" s="47"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A2:K2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="23" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>FY27 signed-backlog execution | priority and earnings</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>Use approved customer priority and contract terms; roll unfinished work rather than manufacturing capacity</x:v>
+      </x:c>
+      <x:c r="B2" s="6"/>
+      <x:c r="C2" s="6"/>
+      <x:c r="D2" s="6"/>
+      <x:c r="E2" s="6"/>
+      <x:c r="F2" s="6"/>
+      <x:c r="G2" s="6"/>
+      <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
+      <x:c r="K2" s="6"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="15" t="str">
+        <x:v>Project</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Signed backlog</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Required hours</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Completed hours</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Deferred hours</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Completed revenue</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Deferred revenue</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>Completed gross profit</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
+        <x:v>Liquidated damages</x:v>
+      </x:c>
+      <x:c r="K4" s="17" t="str">
+        <x:v>Release decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="45" t="str">
+        <x:v>P-3101</x:v>
+      </x:c>
+      <x:c r="B5" s="45"/>
+      <x:c r="C5" s="45"/>
+      <x:c r="D5" s="45"/>
+      <x:c r="E5" s="45"/>
+      <x:c r="F5" s="45"/>
+      <x:c r="G5" s="45"/>
+      <x:c r="H5" s="45"/>
+      <x:c r="I5" s="45"/>
+      <x:c r="J5" s="45"/>
+      <x:c r="K5" s="45"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="46" t="str">
+        <x:v>P-3107</x:v>
+      </x:c>
+      <x:c r="B6" s="46"/>
+      <x:c r="C6" s="46"/>
+      <x:c r="D6" s="46"/>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
+      <x:c r="I6" s="46"/>
+      <x:c r="J6" s="46"/>
+      <x:c r="K6" s="46"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="46" t="str">
+        <x:v>P-3114</x:v>
+      </x:c>
+      <x:c r="B7" s="46"/>
+      <x:c r="C7" s="46"/>
+      <x:c r="D7" s="46"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="46"/>
+      <x:c r="G7" s="46"/>
+      <x:c r="H7" s="46"/>
+      <x:c r="I7" s="46"/>
+      <x:c r="J7" s="46"/>
+      <x:c r="K7" s="46"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="46" t="str">
+        <x:v>P-3122</x:v>
+      </x:c>
+      <x:c r="B8" s="46"/>
+      <x:c r="C8" s="46"/>
+      <x:c r="D8" s="46"/>
+      <x:c r="E8" s="46"/>
+      <x:c r="F8" s="46"/>
+      <x:c r="G8" s="46"/>
+      <x:c r="H8" s="46"/>
+      <x:c r="I8" s="46"/>
+      <x:c r="J8" s="46"/>
+      <x:c r="K8" s="46"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="46" t="str">
+        <x:v>P-3130</x:v>
+      </x:c>
+      <x:c r="B9" s="46"/>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
+      <x:c r="J9" s="46"/>
+      <x:c r="K9" s="46"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="46" t="str">
+        <x:v>P-3138</x:v>
+      </x:c>
+      <x:c r="B10" s="46"/>
+      <x:c r="C10" s="46"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="46"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
+      <x:c r="I10" s="46"/>
+      <x:c r="J10" s="46"/>
+      <x:c r="K10" s="46"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="46" t="str">
+        <x:v>P-3145</x:v>
+      </x:c>
+      <x:c r="B11" s="46"/>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
+      <x:c r="I11" s="46"/>
+      <x:c r="J11" s="46"/>
+      <x:c r="K11" s="46"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="47" t="str">
+        <x:v>P-3152</x:v>
+      </x:c>
+      <x:c r="B12" s="47"/>
+      <x:c r="C12" s="47"/>
+      <x:c r="D12" s="47"/>
+      <x:c r="E12" s="47"/>
+      <x:c r="F12" s="47"/>
+      <x:c r="G12" s="47"/>
+      <x:c r="H12" s="47"/>
+      <x:c r="I12" s="47"/>
+      <x:c r="J12" s="47"/>
+      <x:c r="K12" s="47"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="48" t="str">
+        <x:v>MONTHLY EARNINGS RELEASE BRIDGE</x:v>
+      </x:c>
+      <x:c r="B15" s="48"/>
+      <x:c r="C15" s="48"/>
+      <x:c r="D15" s="48"/>
+      <x:c r="E15" s="48"/>
+      <x:c r="F15" s="48"/>
+      <x:c r="G15" s="48"/>
+      <x:c r="H15" s="48"/>
+      <x:c r="I15" s="48"/>
+      <x:c r="J15" s="48"/>
+      <x:c r="K15" s="48"/>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="15" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Probability-plan GP after response</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>Gross-commitment GP after response</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="str">
+        <x:v>Executable GP after damages</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="str">
+        <x:v>Deferred revenue at risk</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="str">
+        <x:v>Management decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="45" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B17" s="45"/>
+      <x:c r="C17" s="45"/>
+      <x:c r="D17" s="45"/>
+      <x:c r="E17" s="45"/>
+      <x:c r="F17" s="45"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="46" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="B18" s="46"/>
+      <x:c r="C18" s="46"/>
+      <x:c r="D18" s="46"/>
+      <x:c r="E18" s="46"/>
+      <x:c r="F18" s="46"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="46" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B19" s="46"/>
+      <x:c r="C19" s="46"/>
+      <x:c r="D19" s="46"/>
+      <x:c r="E19" s="46"/>
+      <x:c r="F19" s="46"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="46" t="str">
+        <x:v>2026-10</x:v>
+      </x:c>
+      <x:c r="B20" s="46"/>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="46"/>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="46"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="46" t="str">
+        <x:v>2026-11</x:v>
+      </x:c>
+      <x:c r="B21" s="46"/>
+      <x:c r="C21" s="46"/>
+      <x:c r="D21" s="46"/>
+      <x:c r="E21" s="46"/>
+      <x:c r="F21" s="46"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="46" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="B22" s="46"/>
+      <x:c r="C22" s="46"/>
+      <x:c r="D22" s="46"/>
+      <x:c r="E22" s="46"/>
+      <x:c r="F22" s="46"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="46" t="str">
+        <x:v>2027-01</x:v>
+      </x:c>
+      <x:c r="B23" s="46"/>
+      <x:c r="C23" s="46"/>
+      <x:c r="D23" s="46"/>
+      <x:c r="E23" s="46"/>
+      <x:c r="F23" s="46"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="46" t="str">
+        <x:v>2027-02</x:v>
+      </x:c>
+      <x:c r="B24" s="46"/>
+      <x:c r="C24" s="46"/>
+      <x:c r="D24" s="46"/>
+      <x:c r="E24" s="46"/>
+      <x:c r="F24" s="46"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="46" t="str">
+        <x:v>2027-03</x:v>
+      </x:c>
+      <x:c r="B25" s="46"/>
+      <x:c r="C25" s="46"/>
+      <x:c r="D25" s="46"/>
+      <x:c r="E25" s="46"/>
+      <x:c r="F25" s="46"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="46" t="str">
+        <x:v>2027-04</x:v>
+      </x:c>
+      <x:c r="B26" s="46"/>
+      <x:c r="C26" s="46"/>
+      <x:c r="D26" s="46"/>
+      <x:c r="E26" s="46"/>
+      <x:c r="F26" s="46"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="46" t="str">
+        <x:v>2027-05</x:v>
+      </x:c>
+      <x:c r="B27" s="46"/>
+      <x:c r="C27" s="46"/>
+      <x:c r="D27" s="46"/>
+      <x:c r="E27" s="46"/>
+      <x:c r="F27" s="46"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="47" t="str">
+        <x:v>2027-06</x:v>
+      </x:c>
+      <x:c r="B28" s="47"/>
+      <x:c r="C28" s="47"/>
+      <x:c r="D28" s="47"/>
+      <x:c r="E28" s="47"/>
+      <x:c r="F28" s="47"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A2:K2"/>
+    <x:mergeCell ref="A15:K15"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>FY27 backlog and capacity | controls and executive decision</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>One assertion per control; the model is releasable only when the calculations and decision conditions agree</x:v>
+      </x:c>
+      <x:c r="B2" s="6"/>
+      <x:c r="C2" s="6"/>
+      <x:c r="D2" s="6"/>
+      <x:c r="E2" s="6"/>
+      <x:c r="F2" s="6"/>
+      <x:c r="G2" s="6"/>
+      <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
@@ -5632,7 +8909,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
+      <x:c r="A5" s="35" t="str">
         <x:v>Source population tie</x:v>
       </x:c>
       <x:c r="B5" s="35"/>
@@ -5643,75 +8920,156 @@
       <x:c r="G5" s="35"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>Current-versus-prior version</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
-      <x:c r="C6" s="36"/>
-      <x:c r="D6" s="36"/>
-      <x:c r="E6" s="36"/>
-      <x:c r="F6" s="36"/>
-      <x:c r="G6" s="36"/>
+      <x:c r="A6" s="50" t="str">
+        <x:v>Backlog roll-forward</x:v>
+      </x:c>
+      <x:c r="B6" s="50"/>
+      <x:c r="C6" s="50"/>
+      <x:c r="D6" s="50"/>
+      <x:c r="E6" s="50"/>
+      <x:c r="F6" s="50"/>
+      <x:c r="G6" s="50"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>Period completeness</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
-      <x:c r="C7" s="36"/>
-      <x:c r="D7" s="36"/>
-      <x:c r="E7" s="36"/>
-      <x:c r="F7" s="36"/>
-      <x:c r="G7" s="36"/>
+      <x:c r="A7" s="50" t="str">
+        <x:v>Probability-plan burn</x:v>
+      </x:c>
+      <x:c r="B7" s="50"/>
+      <x:c r="C7" s="50"/>
+      <x:c r="D7" s="50"/>
+      <x:c r="E7" s="50"/>
+      <x:c r="F7" s="50"/>
+      <x:c r="G7" s="50"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>Scenario validity</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
-      <x:c r="C8" s="36"/>
-      <x:c r="D8" s="36"/>
-      <x:c r="E8" s="36"/>
-      <x:c r="F8" s="36"/>
-      <x:c r="G8" s="36"/>
+      <x:c r="A8" s="50" t="str">
+        <x:v>Gross-commitment burn</x:v>
+      </x:c>
+      <x:c r="B8" s="50"/>
+      <x:c r="C8" s="50"/>
+      <x:c r="D8" s="50"/>
+      <x:c r="E8" s="50"/>
+      <x:c r="F8" s="50"/>
+      <x:c r="G8" s="50"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>Unit conversion</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
-      <x:c r="C9" s="36"/>
-      <x:c r="D9" s="36"/>
-      <x:c r="E9" s="36"/>
-      <x:c r="F9" s="36"/>
-      <x:c r="G9" s="36"/>
+      <x:c r="A9" s="50" t="str">
+        <x:v>Capacity sign convention</x:v>
+      </x:c>
+      <x:c r="B9" s="50"/>
+      <x:c r="C9" s="50"/>
+      <x:c r="D9" s="50"/>
+      <x:c r="E9" s="50"/>
+      <x:c r="F9" s="50"/>
+      <x:c r="G9" s="50"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>Roll-forward / bridge</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
-      <x:c r="C10" s="36"/>
-      <x:c r="D10" s="36"/>
-      <x:c r="E10" s="36"/>
-      <x:c r="F10" s="36"/>
-      <x:c r="G10" s="36"/>
+      <x:c r="A10" s="50" t="str">
+        <x:v>Remediation sequence</x:v>
+      </x:c>
+      <x:c r="B10" s="50"/>
+      <x:c r="C10" s="50"/>
+      <x:c r="D10" s="50"/>
+      <x:c r="E10" s="50"/>
+      <x:c r="F10" s="50"/>
+      <x:c r="G10" s="50"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="34" t="str">
+      <x:c r="A11" s="50" t="str">
+        <x:v>Project-to-month roll-forward</x:v>
+      </x:c>
+      <x:c r="B11" s="50"/>
+      <x:c r="C11" s="50"/>
+      <x:c r="D11" s="50"/>
+      <x:c r="E11" s="50"/>
+      <x:c r="F11" s="50"/>
+      <x:c r="G11" s="50"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="50" t="str">
+        <x:v>Revenue and gross-profit bridge</x:v>
+      </x:c>
+      <x:c r="B12" s="50"/>
+      <x:c r="C12" s="50"/>
+      <x:c r="D12" s="50"/>
+      <x:c r="E12" s="50"/>
+      <x:c r="F12" s="50"/>
+      <x:c r="G12" s="50"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="36" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="B11" s="37"/>
-      <x:c r="C11" s="37"/>
-      <x:c r="D11" s="37"/>
-      <x:c r="E11" s="37"/>
-      <x:c r="F11" s="37"/>
-      <x:c r="G11" s="37"/>
+      <x:c r="B13" s="36"/>
+      <x:c r="C13" s="36"/>
+      <x:c r="D13" s="36"/>
+      <x:c r="E13" s="36"/>
+      <x:c r="F13" s="36"/>
+      <x:c r="G13" s="36"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="48" t="str">
+        <x:v>EXECUTIVE RECOVERY DECISION</x:v>
+      </x:c>
+      <x:c r="B16" s="48"/>
+      <x:c r="C16" s="48"/>
+      <x:c r="D16" s="48"/>
+      <x:c r="E16" s="48"/>
+      <x:c r="F16" s="48"/>
+      <x:c r="G16" s="48"/>
+      <x:c r="H16" s="48"/>
+      <x:c r="I16" s="48"/>
+      <x:c r="J16" s="48"/>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="15" t="str">
+        <x:v>Recommendation</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="str">
+        <x:v>Probability-plan GP</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="str">
+        <x:v>Gross-commitment GP</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="str">
+        <x:v>Executable GP after damages</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="str">
+        <x:v>Deferred revenue</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="str">
+        <x:v>Deferred gross profit</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="str">
+        <x:v>Damages</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str">
+        <x:v>Recovery required</x:v>
+      </x:c>
+      <x:c r="I17" s="16" t="str">
+        <x:v>Priority item</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="str">
+        <x:v>Release condition / owner action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="51"/>
+      <x:c r="B18" s="51"/>
+      <x:c r="C18" s="51"/>
+      <x:c r="D18" s="51"/>
+      <x:c r="E18" s="51"/>
+      <x:c r="F18" s="51"/>
+      <x:c r="G18" s="51"/>
+      <x:c r="H18" s="51"/>
+      <x:c r="I18" s="51"/>
+      <x:c r="J18" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A16:J16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
